--- a/.skills/visual-design-director/data/theme.xlsx
+++ b/.skills/visual-design-director/data/theme.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="theme_resource_prod" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,141 +425,141 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA94"/>
+  <dimension ref="A1:AA156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>resource_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>resource_type</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>publish_status</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>creator_name</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>created_by</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>deleted_at</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>deleted_by</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>update_seq</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>remark</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>data.title</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>data.description</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>data.id</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>data.order</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>data.colors</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>data.support_app_types</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>data.icon</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>data.image</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>data.is_published_to_prod</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>data.published_to_prod_at</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>data.context</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>data.created_at</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>data.updated_at</t>
         </is>
@@ -3848,7 +3860,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>打造高端、大气、具有礼仪感的节日体验，适合正式祝福。</t>
+          <t>故宫红底，赤金与胭脂红叠搭，马山正书法标题，以喜庆色彩与礼仪感营造节日氛围。</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -3890,7 +3902,7 @@
       <c r="Y21" t="inlineStr">
         <is>
           <t>主题名: 红色喜庆
-主题描述：打造高端、大气、具有礼仪感的节日体验，适合正式祝福。
+主题描述：故宫红底，赤金与胭脂红叠搭，马山正书法标题，以喜庆色彩与礼仪感营造节日氛围。
 色彩：
 - 背景: 故宫红 (#8E1818) 
 - 主色: 赤金 (#D4AF37), 胭脂红 (#C91F37)
@@ -10339,7 +10351,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>打造高端、大气、具有礼仪感的节日体验，适合正式祝福。</t>
+          <t>故宫红底，赤金与胭脂红叠搭，马山正书法标题，以喜庆色彩与礼仪感营造节日氛围。</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
@@ -10381,7 +10393,7 @@
       <c r="Y64" t="inlineStr">
         <is>
           <t>主题名: 红色喜庆
-主题描述：打造高端、大气、具有礼仪感的节日体验，适合正式祝福。
+主题描述：故宫红底，赤金与胭脂红叠搭，马山正书法标题，以喜庆色彩与礼仪感营造节日氛围。
 色彩：
 - 背景: 故宫红 (#8E1818) 
 - 主色: 赤金 (#D4AF37), 胭脂红 (#C91F37)
@@ -10476,7 +10488,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>打造高端、大气、具有礼仪感的节日体验，适合正式祝福。</t>
+          <t>故宫红底，赤金与胭脂红叠搭，马山正书法标题，以喜庆色彩与礼仪感营造节日氛围。</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -10513,7 +10525,7 @@
       <c r="Y65" t="inlineStr">
         <is>
           <t>主题名: 红色喜庆
-主题描述：打造高端、大气、具有礼仪感的节日体验，适合正式祝福。
+主题描述：故宫红底，赤金与胭脂红叠搭，马山正书法标题，以喜庆色彩与礼仪感营造节日氛围。
 色彩：
 - 背景: 故宫红 (#8E1818) 
 - 主色: 赤金 (#D4AF37), 胭脂红 (#C91F37)
@@ -14677,6 +14689,4181 @@
         </is>
       </c>
     </row>
+    <row r="95">
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>多巴胺</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>高饱和霓虹配色，超大胆排版，圆润组件与弹性反馈共同营造快乐、兴奋、充满能量的视觉体验。</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="W95" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Theme Name: 多巴胺
+# Vibe &amp; Description:
+高饱和霓虹配色，超大胆排版，圆润组件与弹性反馈共同营造快乐、兴奋、充满能量的视觉体验。
+# Color
+- 使用 5-6 种高饱和颜色，避免灰色、低饱和色和马卡龙色。
+- 主色使用霓虹粉（#ff006e），辅助色使用紫色（#8338ec），点缀色可使用黄色（#ffbe0b）、蓝色（#3a86ff）、青色（#06d6a0）和橙色（#fb5607）。背景优先使用高饱和色块或 `bg-gradient-to-br from-pink-500 via-purple-500 to-blue-500` 渐变，文字使用深色（#1a1a2e）或白色，保持强烈对比。
+# Font
+- 标题使用 优设标题黑字体，字重必须足够厚重，推荐 （https://resource-static.bj.bcebos.com/fonts-skill/YouSheBiaoTiHei_Regular.ttf）
+- 正文使用 阿里巴巴普惠体3.0 字体（https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf）
+## 字体引入方式
+在 `app/_layout.tsx` 中保持默认系统字体即可
+```js
+import { useFonts } from 'expo-font';
+const [fontsLoaded] = useFonts({
+  'YouSheBiaoTiHei-Regular': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/YouSheBiaoTiHei_Regular.ttf' },
+  'AlibabaPuHuiTi-Regular': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf' },
+});
+```
+`tailwind.config.js` 添加 fontFamily 属性扩展字体
+```js
+{
+  fontFamily: {
+    'youshe-title': ['YouSheBiaoTiHei-Regular', 'sans-serif'],
+    'alibaba-puhuiti-body': ['AlibabaPuHuiTi-Regular', 'sans-serif'],
+  }
+}
+```
+## 字体使用示例
+```jsx
+&lt;Text className="font-youshe-title text-3xl"&gt;&lt;/Text&gt;
+&lt;Text className="font-alibaba-puhuiti-body text-base"&gt;&lt;/Text&gt;
+```
+# Animation
+- 触摸时元素产生明显的弹性反馈，使用 `active:scale-95` 或轻微压缩，让交互有实体碰撞感。
+- Hover 或按压反馈应快速、直接、愉快，可使用 `hover:scale-105`、`hover:-translate-y-0.5` 与 `transition-all duration-300`，避免柔和淡入和模糊景深效果。
+# Layout
+- 页面采用强对比、强分隔和清晰对齐，允许可控的不对称布局，让视觉更活跃。
+- Hero 区使用超大标题、霓虹渐变背景、pill 形 CTA 和趣味 emoji；内容区使用 3-4 个圆润卡片形成节奏，数据区用大号彩色数字强化冲击力。
+# Elements
+- 按钮使用 `rounded-full px-8 py-3 font-bold`，背景采用霓虹粉、紫、蓝或黄，并叠加彩色阴影。
+- 卡片使用 `rounded-3xl p-6`，背景可为白色或高饱和渐变，阴影使用彩色光晕，如 `shadow-[0_8px_30px_rgba(255,0,110,0.4)]`。
+- 输入框使用 `rounded-2xl border-2`，聚焦时切换为彩色边框与柔和霓虹描边。
+- 装饰元素可使用 bubble、pill、emoji、彩色光斑和大圆角色块，整体保持快乐、醒目、能量充沛。
+</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>多巴胺</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>高饱和霓虹配色，超大胆排版，圆润组件与弹性反馈共同营造快乐、兴奋、充满能量的视觉体验。</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Web, MiniProgram</t>
+        </is>
+      </c>
+      <c r="W96" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t># Theme Name: 多巴胺
+# Vibe &amp; Description:
+高饱和霓虹配色，超大胆排版，圆润组件与弹性反馈共同营造快乐、兴奋、充满能量的视觉体验。
+# Color
+- 使用 5-6 种高饱和颜色，避免灰色、低饱和色和马卡龙色。
+- 主色使用霓虹粉（#ff006e），辅助色使用紫色（#8338ec），点缀色可使用黄色（#ffbe0b）、蓝色（#3a86ff）、青色（#06d6a0）和橙色（#fb5607）。背景优先使用高饱和色块或 `bg-gradient-to-br from-pink-500 via-purple-500 to-blue-500` 渐变，文字使用深色（#1a1a2e）或白色，保持强烈对比。
+# Font
+- 标题使用 优设标题黑字体，字重必须足够厚重，推荐 （https://resource-static.bj.bcebos.com/fonts-skill/YouSheBiaoTiHei_Regular.ttf）
+- 正文使用 阿里巴巴普惠体3.0 字体（https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf）
+# Animation
+- 触摸时元素产生明显的弹性反馈，使用 `active:scale-95` 或轻微压缩，让交互有实体碰撞感。
+- Hover 或按压反馈应快速、直接、愉快，可使用 `hover:scale-105`、`hover:-translate-y-0.5` 与 `transition-all duration-300`，避免柔和淡入和模糊景深效果。
+# Layout
+- 页面采用强对比、强分隔和清晰对齐，允许可控的不对称布局，让视觉更活跃。
+- Hero 区使用超大标题、霓虹渐变背景、pill 形 CTA 和趣味 emoji；内容区使用 3-4 个圆润卡片形成节奏，数据区用大号彩色数字强化冲击力。
+# Elements
+- 按钮使用 `rounded-full px-8 py-3 font-bold`，背景采用霓虹粉、紫、蓝或黄，并叠加彩色阴影。
+- 卡片使用 `rounded-3xl p-6`，背景可为白色或高饱和渐变，阴影使用彩色光晕，如 `shadow-[0_8px_30px_rgba(255,0,110,0.4)]`。
+- 输入框使用 `rounded-2xl border-2`，聚焦时切换为彩色边框与柔和霓虹描边。
+- 装饰元素可使用 bubble、pill、emoji、彩色光斑和大圆角色块，整体保持快乐、醒目、能量充沛。</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>浮世绘数字风</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>日本浮世绘木版画语感，靛蓝轮廓、朱红点缀、金叶强调，扁平分区与波浪纹样结合，呈现东方留白和现代数字界面的秩序感。</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="W97" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Theme Name: 浮世绘数字风
+# Vibe &amp; Description:
+日本浮世绘木版画语感，靛蓝轮廓、朱红点缀、金叶强调，扁平分区与波浪纹样结合，呈现东方留白和现代数字界面的秩序感。
+# Color
+- 使用和纸米白、靛蓝、朱红与金叶作为核心色彩，避免渐变、透明玻璃和柔和模糊。
+- 背景使用米白色（#F5F0E1），模拟和纸质感；主文字和边框使用靛蓝（#1A3055）；强调色使用朱红（#D4553A）与金叶色（#C9A227）。整体色彩应大面积平涂、边界清晰，像木版套色般分明。
+# Font
+- 使用「思源宋体」作为标题字体，强化东方木版画的厚重感。（https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-Bold.woff2）
+- 使用「HarmonyOS Sans」作为正文字体，保持移动端阅读清晰。（https://resource-static.bj.bcebos.com/fonts-skill/HarmonyOSSans_Regular.ttf）
+## 字体引入方式
+在 `app/_layout.tsx` 中加载字体
+```js
+import { useFonts } from 'expo-font';
+const [fontsLoaded] = useFonts({
+  'SourceHanSerifCN-Bold': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-Bold.woff2' },
+  'HarmonyOSSans-Regular': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/HarmonyOSSans_Regular.ttf' },
+});
+```
+`tailwind.config.js` 添加 fontFamily 属性扩展字体
+```js
+{
+  fontFamily: {
+    'serif-title': ['SourceHanSerifCN-Bold', 'serif'],
+    'harmony-body': ['HarmonyOSSans-Regular', 'sans-serif'],
+  }
+}
+```
+## 字体使用示例
+```jsx
+&lt;Text className="font-serif-title text-3xl"&gt;&lt;/Text&gt;
+&lt;Text className="font-harmony-body text-base"&gt;&lt;/Text&gt;
+```
+# Animation
+- 触摸时元素轻微上浮，阴影从硬边小块变为更重的版画压印感；点击时向下回落，模拟纸面被按压。
+- 页面元素出现时使用短促的淡入与轻微位移，不使用弹性、玻璃感或柔光动效，保持沉稳克制。
+# Layout
+- 采用扁平层叠构图，弱化景深，通过色块、粗边框和留白建立层级。
+- 移动端以单列卡片为主，标题大而醒目，内容区保持宽松间距；分割线使用粗靛蓝边框，形成木版画般的结构感。
+# Elements
+- 按钮和卡片使用 `border-2 border-[#1A3055] rounded-sm`，搭配硬边阴影如 `shadow-[4px_4px_0px_#1A3055]`。
+- 装饰元素使用波浪、山川、花鸟或朱红印章式点缀，但数量克制，避免喧宾夺主。
+- 卡片背景保持米白色，标题使用靛蓝粗体宽字距，重点信息可用朱红或金叶色标记。
+- 所有圆角保持小幅度硬边效果，避免 `rounded-full`、大圆角按钮和西式柔和卡片。
+</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>浮世绘数字风</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>日本浮世绘木版画语感，靛蓝轮廓、朱红点缀、金叶强调，扁平分区与波浪纹样结合，呈现东方留白和现代数字界面的秩序感。</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Web, MiniProgram</t>
+        </is>
+      </c>
+      <c r="W98" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t># Theme Name: 浮世绘数字风
+# Vibe &amp; Description:
+日本浮世绘木版画语感，靛蓝轮廓、朱红点缀、金叶强调，扁平分区与波浪纹样结合，呈现东方留白和现代数字界面的秩序感。
+# Color
+- 使用和纸米白、靛蓝、朱红与金叶作为核心色彩，避免渐变、透明玻璃和柔和模糊。
+- 背景使用米白色（#F5F0E1），模拟和纸质感；主文字和边框使用靛蓝（#1A3055）；强调色使用朱红（#D4553A）与金叶色（#C9A227）。整体色彩应大面积平涂、边界清晰，像木版套色般分明。
+# Font
+- 使用「思源宋体」作为标题字体，强化东方木版画的厚重感。（https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-Bold.woff2）
+- 使用「HarmonyOS Sans」作为正文字体，保持移动端阅读清晰。（https://resource-static.bj.bcebos.com/fonts-skill/HarmonyOSSans_Regular.ttf）
+# Animation
+- 触摸时元素轻微上浮，阴影从硬边小块变为更重的版画压印感；点击时向下回落，模拟纸面被按压。
+- 页面元素出现时使用短促的淡入与轻微位移，不使用弹性、玻璃感或柔光动效，保持沉稳克制。
+# Layout
+- 采用扁平层叠构图，弱化景深，通过色块、粗边框和留白建立层级。
+- 移动端以单列卡片为主，标题大而醒目，内容区保持宽松间距；分割线使用粗靛蓝边框，形成木版画般的结构感。
+# Elements
+- 按钮和卡片使用 `border-2 border-[#1A3055] rounded-sm`，搭配硬边阴影如 `shadow-[4px_4px_0px_#1A3055]`。
+- 装饰元素使用波浪、山川、花鸟或朱红印章式点缀，但数量克制，避免喧宾夺主。
+- 卡片背景保持米白色，标题使用靛蓝粗体宽字距，重点信息可用朱红或金叶色标记。
+- 所有圆角保持小幅度硬边效果，避免 `rounded-full`、大圆角按钮和西式柔和卡片。</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>HUD工业风</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>曜石黑底，霓虹橙激光线，等宽字体与仪表盘刻度，模拟工业级渲染控制台的紧张感与机械感。</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="W99" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Theme Name: HUD工业风
+# Vibe &amp; Description:
+曜石黑底，霓虹橙激光线，等宽字体与仪表盘刻度，模拟工业级渲染控制台的紧张感与机械感。
+# Color
+- 严格限制色彩，仅使用极黑、深灰、浅灰和霓虹橙。
+- 背景使用曜石黑（#020202），面板使用深黑灰（#0A0A0A），文字使用浅灰（#E0E0E0），辅助信息使用中灰（#888888）。强调色仅使用霓虹橙（#FF4500），用于关键数值、进度、激光线和交互反馈，形成“黑暗仪器中唯一生命信号”的视觉感受。
+# Font
+- 使用「站酷酷黑体」作为标题字体。（https://resource-static.bj.bcebos.com/fonts-skill/ZCOOLKuHei_Regular.ttf）
+- 使用「阿里巴巴普惠体3.0」作为正文字体。（https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf）
+## 字体引入方式
+在 `app/_layout.tsx` 中加载字体
+```js
+import { useFonts } from 'expo-font';
+const [fontsLoaded] = useFonts({
+  'ZCOOLKuHei-Regular': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/ZCOOLKuHei_Regular.ttf' },
+  'AlibabaPuHuiTi-Regular': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf' },
+});
+```
+`tailwind.config.js` 添加 fontFamily 属性扩展字体
+```js
+{
+  fontFamily: {
+    'title-zkkh': ['ZCOOLKuHei-Regular', 'sans-serif'],
+    'body-alibaba-puhuiti': ['AlibabaPuHuiTi-Regular', 'sans-serif'],
+  }
+}
+```
+## 字体使用示例
+```jsx
+&lt;Text className="font-title-zkkh text-3xl"&gt;&lt;/Text&gt;
+&lt;Text className="font-body-alibaba-puhuiti text-base"&gt;&lt;/Text&gt;
+```
+# Animation
+- 触摸时元素不做柔和弹性反馈，而是产生短促、精确的机械响应：边框变为霓虹橙、轻微上移、按下时略微压缩。
+- 数据出现时采用进度条填充、日志滚动、激光呼吸等动画，保持冷静克制，只强化状态变化，不制造装饰性动效。
+# Layout
+- 页面采用高密度、无留白的控制台式布局，区块紧密衔接，边框直接分割信息区域。
+- 使用顶部状态栏、核心视觉区、任务列表、节点日志和集群卡片形成明确层级。移动端保留纵向堆叠结构，确保信息紧凑但可读。
+# Elements
+- 卡片、表格、日志面板全部使用直角边框，禁止圆角和阴影，边框统一为 #333333。
+- 进度条、关键数值、活动状态统一使用 #FF4500，避免出现其他高饱和色。
+- 背景可叠加细微颗粒噪点，模拟工业屏幕与胶片质感。
+- 视觉焦点可使用 CSS 绘制黑曜石球体与橙色激光线，强化虚空渲染与高端 VFX 控制台气质。
+</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>HUD工业风</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>曜石黑底，霓虹橙激光线，等宽字体与仪表盘刻度，模拟工业级渲染控制台的紧张感与机械感。</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Web, MiniProgram</t>
+        </is>
+      </c>
+      <c r="W100" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t># Theme Name: HUD工业风
+# Vibe &amp; Description:
+曜石黑底，霓虹橙激光线，等宽字体与仪表盘刻度，模拟工业级渲染控制台的紧张感与机械感。
+# Color
+- 严格限制色彩，仅使用极黑、深灰、浅灰和霓虹橙。
+- 背景使用曜石黑（#020202），面板使用深黑灰（#0A0A0A），文字使用浅灰（#E0E0E0），辅助信息使用中灰（#888888）。强调色仅使用霓虹橙（#FF4500），用于关键数值、进度、激光线和交互反馈，形成“黑暗仪器中唯一生命信号”的视觉感受。
+# Font
+- 使用「站酷酷黑体」作为标题字体。（https://resource-static.bj.bcebos.com/fonts-skill/ZCOOLKuHei_Regular.ttf）
+- 使用「阿里巴巴普惠体3.0」作为正文字体。（https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf）
+# Animation
+- 触摸时元素不做柔和弹性反馈，而是产生短促、精确的机械响应：边框变为霓虹橙、轻微上移、按下时略微压缩。
+- 数据出现时采用进度条填充、日志滚动、激光呼吸等动画，保持冷静克制，只强化状态变化，不制造装饰性动效。
+# Layout
+- 页面采用高密度、无留白的控制台式布局，区块紧密衔接，边框直接分割信息区域。
+- 使用顶部状态栏、核心视觉区、任务列表、节点日志和集群卡片形成明确层级。移动端保留纵向堆叠结构，确保信息紧凑但可读。
+# Elements
+- 卡片、表格、日志面板全部使用直角边框，禁止圆角和阴影，边框统一为 #333333。
+- 进度条、关键数值、活动状态统一使用 #FF4500，避免出现其他高饱和色。
+- 背景可叠加细微颗粒噪点，模拟工业屏幕与胶片质感。
+- 视觉焦点可使用 CSS 绘制黑曜石球体与橙色激光线，强化虚空渲染与高端 VFX 控制台气质。</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>复古胶片</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>暗黑电影志，地下出版物质感，融合剪辑控制台、技术日志、胶片颗粒与高密度信息排版，整体冷峻、工业、紧凑。</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="W101" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Theme Name: 复古胶片
+# Vibe &amp; Description:
+暗黑电影志，地下出版物质感，融合剪辑控制台、技术日志、胶片颗粒与高密度信息排版，整体冷峻、工业、紧凑。
+# Color
+- 严格限制色彩，仅使用深焦糖黑、深石板灰、暖骨白、灰棕文字和电光橙。
+- 背景使用 #12100E，模块使用 #1A1714 / #1C1916，文字使用 #D9D2C5，辅助信息使用 #A0988C。强调色仅使用 #FF4500，用于编号、状态点、按钮边框和粗分隔线。
+- 禁止纯白、纯黑、亮色背景与非橙色高饱和色彩。所有分隔线使用 #2C2824 的 1px 发丝线，重点区域可使用 #FF4500 的 4px 粗条。
+# Font
+- 使用「沐瑶软笔手写体」作为标题字体。（https://resource-static.bj.bcebos.com/fonts-skill/MuyaoSoftbrush_Regular.ttf）
+- 使用「思源宋体」作为正文、日志和元数据字体。（https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-Regular.woff2）
+## 字体引入方式
+在 `app/_layout.tsx` 中加载字体
+```js
+import { useFonts } from 'expo-font';
+const [fontsLoaded] = useFonts({
+  'MuyaoSoftbrush-Regular': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/MuyaoSoftbrush_Regular.ttf' },
+  'SourceHanSerifCN-Regular': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-Regular.woff2' },
+});
+```
+`tailwind.config.js` 添加 fontFamily 属性扩展字体
+```js
+{
+  fontFamily: {
+    'title-muyao': ['MuyaoSoftbrush-Regular', 'sans-serif'],
+    'body-serif': ['SourceHanSerifCN-Regular', 'serif'],
+  }
+}
+```
+## 字体使用示例
+```jsx
+&lt;Text className="font-title-muyao text-3xl"&gt;&lt;/Text&gt;
+&lt;Text className="font-body-serif text-base"&gt;&lt;/Text&gt;
+```
+# Animation
+- 仅保留克制的系统反馈：状态圆点以短促闪烁呈现“实时会话”，列表项触摸时背景切换为 #2A2520。
+- 按钮点击可使用轻微按压反馈，避免弹跳、旋转或装饰性动效。所有过渡保持快速、硬朗、工业化。
+# Layout
+- 页面采用暗色紧凑信息流，上方固定 48px 控制栏，展示微型导航、期号标签、实时状态和操作员信息。
+- 首屏使用超大压缩标题与电影静帧，图片叠加灰度、对比度和颗粒滤镜，下方放置剪辑序列式副标题。
+- 主体内容以密集卡片排列，每个模块包含巨大橙色编号、短技术段落和发丝分隔线。侧向索引在移动端转为纵向日志列表，条目包含时间戳、标题、缩略块和“进入”按钮。
+- 所有区块直角、无阴影、低留白，边框紧密衔接，形成剪辑软件与渲染农场控制台的界面感。
+# Elements
+- 卡片、按钮、列表、状态面板全部使用直角边框，禁止圆角和投影。
+- 使用十字瞄准标记、1px 坐标线、REC 标识、时间码、FPS、LUT、LOG-C 等技术元数据增强电影后期语境。
+- 背景叠加细微胶片噪点，图片可使用灰度、低亮度和高对比滤镜，模拟老旧监视器与胶片放映。
+- 滚动条、编号、按钮描边和关键状态统一使用 #FF4500，其他信息保持暖骨白与灰棕层级。
+</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>复古胶片</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>暗黑电影志，地下出版物质感，融合剪辑控制台、技术日志、胶片颗粒与高密度信息排版，整体冷峻、工业、紧凑。</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Web, MiniProgram</t>
+        </is>
+      </c>
+      <c r="W102" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t># Theme Name: 复古胶片
+# Vibe &amp; Description:
+暗黑电影志，地下出版物质感，融合剪辑控制台、技术日志、胶片颗粒与高密度信息排版，整体冷峻、工业、紧凑。
+# Color
+- 严格限制色彩，仅使用深焦糖黑、深石板灰、暖骨白、灰棕文字和电光橙。
+- 背景使用 #12100E，模块使用 #1A1714 / #1C1916，文字使用 #D9D2C5，辅助信息使用 #A0988C。强调色仅使用 #FF4500，用于编号、状态点、按钮边框和粗分隔线。
+- 禁止纯白、纯黑、亮色背景与非橙色高饱和色彩。所有分隔线使用 #2C2824 的 1px 发丝线，重点区域可使用 #FF4500 的 4px 粗条。
+# Font
+- 使用「沐瑶软笔手写体」作为标题字体。（https://resource-static.bj.bcebos.com/fonts-skill/MuyaoSoftbrush_Regular.ttf）
+- 使用「思源宋体」作为正文、日志和元数据字体。（https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-Regular.woff2）
+# Animation
+- 仅保留克制的系统反馈：状态圆点以短促闪烁呈现“实时会话”，列表项触摸时背景切换为 #2A2520。
+- 按钮点击可使用轻微按压反馈，避免弹跳、旋转或装饰性动效。所有过渡保持快速、硬朗、工业化。
+# Layout
+- 页面采用暗色紧凑信息流，上方固定 48px 控制栏，展示微型导航、期号标签、实时状态和操作员信息。
+- 首屏使用超大压缩标题与电影静帧，图片叠加灰度、对比度和颗粒滤镜，下方放置剪辑序列式副标题。
+- 主体内容以密集卡片排列，每个模块包含巨大橙色编号、短技术段落和发丝分隔线。侧向索引在移动端转为纵向日志列表，条目包含时间戳、标题、缩略块和“进入”按钮。
+- 所有区块直角、无阴影、低留白，边框紧密衔接，形成剪辑软件与渲染农场控制台的界面感。
+# Elements
+- 卡片、按钮、列表、状态面板全部使用直角边框，禁止圆角和投影。
+- 使用十字瞄准标记、1px 坐标线、REC 标识、时间码、FPS、LUT、LOG-C 等技术元数据增强电影后期语境。
+- 背景叠加细微胶片噪点，图片可使用灰度、低亮度和高对比滤镜，模拟老旧监视器与胶片放映。
+- 滚动条、编号、按钮描边和关键状态统一使用 #FF4500，其他信息保持暖骨白与灰棕层级。</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>轻奢度假风</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>极简奢华，思源宋体大标题，暖金细线点缀，以大量留白、克制排版和高质感酒店摄影营造安静、私享、沉浸的度假氛围。</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="W103" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Theme Name: 轻奢度假风
+# Vibe &amp; Description:
+极简奢华，思源宋体大标题，暖金细线点缀，以大量留白、克制排版和高质感酒店摄影营造安静、私享、沉浸的度假氛围。
+# Color
+- 色彩保持克制，仅使用深海军蓝、纯白、米白、暖金和中灰。
+- 背景以纯白（#FFFFFF）和温暖米白（#F8F7F4）为主，文字使用深海军蓝（#1A1A2E），辅助文字使用中灰（#888888）。暖金（#C9A96E）只作为评分、徽章、hover 和细节点缀，传达低调奢华感。
+- CTA 可使用近黑色（#1A1A1A）搭配白色文字，避免渐变、高饱和色和过度装饰。
+# Font
+- 使用「思源宋体」作为标题字体，营造建筑杂志般的高级感。（https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-Bold.woff2）
+- 使用「阿里巴巴普惠体3.0」作为正文字体，保持清晰、克制和现代感。（https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf）
+## 字体引入方式
+在 `app/_layout.tsx` 中加载字体
+```js
+import { useFonts } from 'expo-font';
+const [fontsLoaded] = useFonts({
+  'SourceHanSerifCN-Bold': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-Bold.woff2' },
+  'AlibabaPuHuiTi-Regular': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf' },
+});
+```
+`tailwind.config.js` 添加 fontFamily 属性扩展字体
+```js
+{
+  fontFamily: {
+    'title-serif-bold': ['SourceHanSerifCN-Bold', 'serif'],
+    'body-alibaba': ['AlibabaPuHuiTi-Regular', 'sans-serif'],
+  }
+}
+```
+## 字体使用示例
+```jsx
+&lt;Text className="font-title-serif-bold text-3xl"&gt;&lt;/Text&gt;
+&lt;Text className="font-body-alibaba text-base"&gt;&lt;/Text&gt;
+```
+# Animation
+- 卡片触摸时轻微上浮并增强阴影，点击按钮时有细微缩放反馈，保持安静、克制。
+- 页面内容出现时采用淡入和轻微位移，统计数字可在进入视口后递增，避免弹跳、旋转等花哨动效。
+# Layout
+- 页面强调大留白和清晰层级，标题大而克制，正文短句排布，整体像高端建筑与旅行杂志。
+- mobile app 中使用单列沉浸式布局：顶部以大幅酒店建筑摄影建立氛围，下方通过精选酒店卡片、体验功能、用户评价和订阅模块逐步展开。
+- 卡片之间保持充足间距，界面本身尽量退后，让建筑摄影、空间光影和文字层级成为主角。
+# Elements
+- 酒店卡片使用高质量建筑摄影，图片比例偏竖向，圆角适度，默认轻阴影，触摸时轻微上移。
+- 玻璃信息卡可叠放在 Hero 图片上，使用半透明白、模糊背景和极细白色边框，营造私享行馆感。
+- 功能卡片使用米白背景和大圆角，内容包含简洁图标、标题和短描述。
+- 按钮使用圆角胶囊形，主按钮为近黑底白字，订阅按钮可用白底深色字，hover 或 press 时以暖金作为唯一强调色。
+</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>轻奢度假风</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>极简奢华，思源宋体大标题，暖金细线点缀，以大量留白、克制排版和高质感酒店摄影营造安静、私享、沉浸的度假氛围。</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Web, MiniProgram</t>
+        </is>
+      </c>
+      <c r="W104" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t># Theme Name: 轻奢度假风
+# Vibe &amp; Description:
+极简奢华，思源宋体大标题，暖金细线点缀，以大量留白、克制排版和高质感酒店摄影营造安静、私享、沉浸的度假氛围。
+# Color
+- 色彩保持克制，仅使用深海军蓝、纯白、米白、暖金和中灰。
+- 背景以纯白（#FFFFFF）和温暖米白（#F8F7F4）为主，文字使用深海军蓝（#1A1A2E），辅助文字使用中灰（#888888）。暖金（#C9A96E）只作为评分、徽章、hover 和细节点缀，传达低调奢华感。
+- CTA 可使用近黑色（#1A1A1A）搭配白色文字，避免渐变、高饱和色和过度装饰。
+# Font
+- 使用「思源宋体」作为标题字体，营造建筑杂志般的高级感。（https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-Bold.woff2）
+- 使用「阿里巴巴普惠体3.0」作为正文字体，保持清晰、克制和现代感。（https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf）
+# Animation
+- 卡片触摸时轻微上浮并增强阴影，点击按钮时有细微缩放反馈，保持安静、克制。
+- 页面内容出现时采用淡入和轻微位移，统计数字可在进入视口后递增，避免弹跳、旋转等花哨动效。
+# Layout
+- 页面强调大留白和清晰层级，标题大而克制，正文短句排布，整体像高端建筑与旅行杂志。
+- mobile app 中使用单列沉浸式布局：顶部以大幅酒店建筑摄影建立氛围，下方通过精选酒店卡片、体验功能、用户评价和订阅模块逐步展开。
+- 卡片之间保持充足间距，界面本身尽量退后，让建筑摄影、空间光影和文字层级成为主角。
+# Elements
+- 酒店卡片使用高质量建筑摄影，图片比例偏竖向，圆角适度，默认轻阴影，触摸时轻微上移。
+- 玻璃信息卡可叠放在 Hero 图片上，使用半透明白、模糊背景和极细白色边框，营造私享行馆感。
+- 功能卡片使用米白背景和大圆角，内容包含简洁图标、标题和短描述。
+- 按钮使用圆角胶囊形，主按钮为近黑底白字，订阅按钮可用白底深色字，hover 或 press 时以暖金作为唯一强调色。</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>时尚杂志风</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>高端时尚杂志式排版，暖米色纸感背景，柔和黑单色文字，衬线标题与无衬线正文形成优雅对比。强调留白、网格秩序、精细分割线与克制的下划线交互。</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="W105" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Theme Name: 时尚杂志风
+# Vibe &amp; Description:
+高端时尚杂志式排版，暖米色纸感背景，柔和黑单色文字，衬线标题与无衬线正文形成优雅对比。强调留白、网格秩序、精细分割线与克制的下划线交互。
+# Color
+- 严格限制色彩，仅使用暖米色背景与柔和黑文字，不使用任何彩色强调色。
+- 背景使用暖米色 `#F9F8F6`，文字使用柔和黑 `#1C1C1C`。通过透明度建立层级：正文主色为 `#1C1C1C`，次要信息使用 `#1C1C1C99`，辅助说明使用 `#1C1C1C66`，边框与分割线使用 `#1C1C1C1A`。
+- 禁止高饱和色、渐变、纯黑大面积填充、冷白背景、阴影和圆角，整体保持单色、安静、克制。
+# Font
+- 使用「思源宋体」作为标题字体，营造杂志封面般的衬线气质。（https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-SemiBold.woff2）
+- 使用「思源宋体」作为正文字体，保持阅读清晰、现代和轻盈。（https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-Regular.woff2）
+## 字体引入方式
+在 `app/_layout.tsx` 中加载字体
+```js
+import { useFonts } from 'expo-font';
+const [fontsLoaded] = useFonts({
+  'SourceHanSerifCN-SemiBold': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-SemiBold.woff2' },
+  'SourceHanSerifCN-Regular': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-Regular.woff2' },
+});
+```
+`tailwind.config.js` 添加 fontFamily 属性扩展字体
+```js
+{
+  fontFamily: {
+    'title-serif-semibold': ['SourceHanSerifCN-SemiBold', 'serif'],
+    'body-serif': ['SourceHanSerifCN-Regular', 'serif'],
+  }
+}
+```
+## 字体使用示例
+```jsx
+&lt;Text className="font-title-serif-semibold text-3xl"&gt;&lt;/Text&gt;
+&lt;Text className="font-body-serif text-base"&gt;&lt;/Text&gt;
+```
+# Animation
+- 交互保持克制：点击时轻微缩小，链接与按钮使用下划线显现，文字可在 hover / press 状态中呈现轻微斜体感。
+- 图片出现时采用裁切揭示或淡入效果，像杂志翻页时画面被缓慢展开。
+- 列表、归档和作品项进入视野时使用轻微淡入，不使用弹跳、旋转或夸张位移。
+# Layout
+- 页面采用宽松留白和清晰网格，内容之间保持大间距，形成高级杂志的呼吸感。
+- 顶部导航固定，Logo 使用衬线字体；Hero 区使用超大衬线标题、斜体副标题和一张主视觉图。
+- 作品列表以编号、标题、短描述组成，项目之间使用极细分割线；归档内容可采用错落双列，但整体仍需保持秩序与留白。
+# Elements
+- 按钮无填充背景，以文字和下划线作为主要反馈。
+- 输入框使用透明背景和底部分割线，不使用圆角、描边卡片或阴影。
+- 图片以灰度、中性色或低饱和视觉为主，避免彩色装饰抢占文字层级。
+- 页脚使用小字号、uppercase、宽字距和点分隔符，顶部加入极细分割线，保持安静收束。
+</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>时尚杂志风</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>高端时尚杂志式排版，暖米色纸感背景，柔和黑单色文字，衬线标题与无衬线正文形成优雅对比。强调留白、网格秩序、精细分割线与克制的下划线交互。</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Web, MiniProgram</t>
+        </is>
+      </c>
+      <c r="W106" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t># Theme Name: 时尚杂志风
+# Vibe &amp; Description:
+高端时尚杂志式排版，暖米色纸感背景，柔和黑单色文字，衬线标题与无衬线正文形成优雅对比。强调留白、网格秩序、精细分割线与克制的下划线交互。
+# Color
+- 严格限制色彩，仅使用暖米色背景与柔和黑文字，不使用任何彩色强调色。
+- 背景使用暖米色 `#F9F8F6`，文字使用柔和黑 `#1C1C1C`。通过透明度建立层级：正文主色为 `#1C1C1C`，次要信息使用 `#1C1C1C99`，辅助说明使用 `#1C1C1C66`，边框与分割线使用 `#1C1C1C1A`。
+- 禁止高饱和色、渐变、纯黑大面积填充、冷白背景、阴影和圆角，整体保持单色、安静、克制。
+# Font
+- 使用「思源宋体」作为标题字体，营造杂志封面般的衬线气质。（https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-SemiBold.woff2）
+- 使用「思源宋体」作为正文字体，保持阅读清晰、现代和轻盈。（https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-Regular.woff2）
+# Animation
+- 交互保持克制：点击时轻微缩小，链接与按钮使用下划线显现，文字可在 hover / press 状态中呈现轻微斜体感。
+- 图片出现时采用裁切揭示或淡入效果，像杂志翻页时画面被缓慢展开。
+- 列表、归档和作品项进入视野时使用轻微淡入，不使用弹跳、旋转或夸张位移。
+# Layout
+- 页面采用宽松留白和清晰网格，内容之间保持大间距，形成高级杂志的呼吸感。
+- 顶部导航固定，Logo 使用衬线字体；Hero 区使用超大衬线标题、斜体副标题和一张主视觉图。
+- 作品列表以编号、标题、短描述组成，项目之间使用极细分割线；归档内容可采用错落双列，但整体仍需保持秩序与留白。
+# Elements
+- 按钮无填充背景，以文字和下划线作为主要反馈。
+- 输入框使用透明背景和底部分割线，不使用圆角、描边卡片或阴影。
+- 图片以灰度、中性色或低饱和视觉为主，避免彩色装饰抢占文字层级。
+- 页脚使用小字号、uppercase、宽字距和点分隔符，顶部加入极细分割线，保持安静收束。</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>印刷风</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>套印错位，半调网点，有限色彩，模拟老式印刷机的粗粝质感与手工批量感。</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="W107" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Theme Name: 印刷风
+# Vibe &amp; Description:
+套印错位，半调网点，有限色彩，模拟老式印刷机的粗粝质感与手工批量感。
+# Color
+- 严格限制色彩，仅使用纸白、粗黑、粉红和蓝色，少量橙色作为强调。
+- 背景使用纸白色（#FDFBF7），文字与边框使用粗黑色（#1A1A1A），主色使用印刷粉（#FF6B9D），辅助色使用蓝色（#2563EB）。禁止渐变，所有色块保持扁平、硬边、直接。
+# Font
+- 使用「优设标题黑」作为标题字体。（https://resource-static.bj.bcebos.com/fonts-skill/YouSheBiaoTiHei_Regular.ttf）
+- 使用「阿里巴巴普惠体3.0」作为正文字体。（https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf）
+## 字体引入方式
+在 `app/_layout.tsx` 中加载字体
+```js
+import { useFonts } from 'expo-font';
+const [fontsLoaded] = useFonts({
+  'YouSheBiaoTiHei-Regular': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/YouSheBiaoTiHei_Regular.ttf' },
+  'AlibabaPuHuiTi-Regular': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf' },
+});
+```
+`tailwind.config.js` 添加 fontFamily 属性扩展字体
+```js
+{
+  fontFamily: {
+    'title-youshe': ['YouSheBiaoTiHei-Regular', 'sans-serif'],
+    'body-alibaba': ['AlibabaPuHuiTi-Regular', 'sans-serif'],
+  }
+}
+```
+## 字体使用示例
+```jsx
+&lt;Text className="font-title-youshe text-3xl"&gt;&lt;/Text&gt;
+&lt;Text className="font-body-alibaba text-base"&gt;&lt;/Text&gt;
+```
+# Animation
+- 触摸按钮或卡片时，元素向右下轻微位移，硬阴影收缩或消失，模拟印刷纸张被按下的反馈。
+- 元素出现时采用短促的淡入与错位叠印效果，粉色或蓝色阴影略微偏移，制造套印不准的视觉趣味。
+# Layout
+- 页面使用清晰的网格结构，卡片、按钮和导航保持粗黑边框与硬边阴影，整体像一张被分区排版的印刷海报。
+- 移动端以单列为主，留白充足，标题放大并使用大写、等宽、粗体排版，形成强烈的印刷标题感。
+# Elements
+- 按钮和卡片使用 `border-2 border-[#1A1A1A] rounded-sm`，搭配 `shadow-[3px_3px_0px_#FF6B9D]` 形成硬边套印阴影。
+- 背景或卡片局部叠加半调网点纹理，保持低透明度，避免影响阅读。
+- 图标、标签和装饰块使用扁平色块，不使用写实光影、模糊阴影或复杂渐变。
+- 强调文字可使用轻微的粉色或蓝色错位描边，营造印刷套色偏移效果。
+</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>印刷风</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>套印错位，半调网点，有限色彩，模拟老式印刷机的粗粝质感与手工批量感。</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Web, MiniProgram</t>
+        </is>
+      </c>
+      <c r="W108" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t># Theme Name: 印刷风
+# Vibe &amp; Description:
+套印错位，半调网点，有限色彩，模拟老式印刷机的粗粝质感与手工批量感。
+# Color
+- 严格限制色彩，仅使用纸白、粗黑、粉红和蓝色，少量橙色作为强调。
+- 背景使用纸白色（#FDFBF7），文字与边框使用粗黑色（#1A1A1A），主色使用印刷粉（#FF6B9D），辅助色使用蓝色（#2563EB）。禁止渐变，所有色块保持扁平、硬边、直接。
+# Font
+- 使用「优设标题黑」作为标题字体。（https://resource-static.bj.bcebos.com/fonts-skill/YouSheBiaoTiHei_Regular.ttf）
+- 使用「阿里巴巴普惠体3.0」作为正文字体。（https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf）
+# Animation
+- 触摸按钮或卡片时，元素向右下轻微位移，硬阴影收缩或消失，模拟印刷纸张被按下的反馈。
+- 元素出现时采用短促的淡入与错位叠印效果，粉色或蓝色阴影略微偏移，制造套印不准的视觉趣味。
+# Layout
+- 页面使用清晰的网格结构，卡片、按钮和导航保持粗黑边框与硬边阴影，整体像一张被分区排版的印刷海报。
+- 移动端以单列为主，留白充足，标题放大并使用大写、等宽、粗体排版，形成强烈的印刷标题感。
+# Elements
+- 按钮和卡片使用 `border-2 border-[#1A1A1A] rounded-sm`，搭配 `shadow-[3px_3px_0px_#FF6B9D]` 形成硬边套印阴影。
+- 背景或卡片局部叠加半调网点纹理，保持低透明度，避免影响阅读。
+- 图标、标签和装饰块使用扁平色块，不使用写实光影、模糊阴影或复杂渐变。
+- 强调文字可使用轻微的粉色或蓝色错位描边，营造印刷套色偏移效果。</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>像素艺术风</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>复古 8-bit 游戏视觉，硬边轮廓，高饱和像素配色，强调无圆角、粗边框和瞬时反馈，营造经典街机与独立游戏的怀旧感。</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="W109" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Theme Name: 像素艺术风
+# Vibe &amp; Description:
+复古 8-bit 游戏视觉，硬边轮廓，高饱和像素配色，强调无圆角、粗边框和瞬时反馈，营造经典街机与独立游戏的怀旧感。
+# Color
+- 使用经典 8-bit 调色板，避免渐变、透明度过渡和柔和色彩。
+- 背景与边框使用深色像素黑（#1A1C2C），基础背景使用亮白（#F4F4F4），强调色使用红（#FF004D）、绿（#00E436）、蓝（#29ADFF）、黄（#FFEC27）。整体色彩应直接、鲜明、高对比，像早期游戏界面一样清晰有力。
+# Font
+- 使用「寒蝉点阵体16px」作为标题字体。（https://resource-static.bj.bcebos.com/fonts-skill/ChillBitmap_16px.ttf）
+- 使用「阿里巴巴普惠体3.0」作为正文字体。（https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf）
+## 字体引入方式
+在 `app/_layout.tsx` 中加载字体
+```js
+import { useFonts } from 'expo-font';
+const [fontsLoaded] = useFonts({
+  'ChillBitmap-16px': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/ChillBitmap_16px.ttf' },
+  'AlibabaPuHuiTi-Regular': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf' },
+});
+```
+`tailwind.config.js` 添加 fontFamily 属性扩展字体
+```js
+{
+  fontFamily: {
+    'title-hanchandianzhen': ['ChillBitmap-16px', 'monospace'],
+    'body-alibaba': ['AlibabaPuHuiTi-Regular', 'sans-serif'],
+  }
+}
+```
+## 字体使用示例
+```jsx
+&lt;Text className="font-title-hanchandianzhen text-3xl"&gt;&lt;/Text&gt;
+&lt;Text className="font-body-alibaba text-base"&gt;&lt;/Text&gt;
+```
+# Animation
+- 所有交互采用瞬时硬切，不使用缓动、渐变或透明度动画。触摸时元素向右下移动 1-2px，同时阴影缩短或消失，形成“按下实体按钮”的反馈。
+- Hover 或选中状态采用 Palette Swap，直接切换为另一种 8-bit 强调色，如红色按钮切换为蓝色，不保留中间过渡状态。
+# Layout
+- 页面结构清晰分块，使用粗边框和硬边阴影建立层级。卡片、按钮、输入框均保持方正外观，禁止圆角。
+- mobile app 中保持紧凑但有节奏的网格排布，模块间距明确，重点区域可使用黄色标题、红色行动按钮和蓝绿色状态点缀。
+# Elements
+- 按钮使用 `border-4`、`rounded-none` 和 `shadow-[4px_4px_0_#1a1c2c]`，点击时位移并取消阴影。
+- 卡片使用白底、深色粗边框和硬边阴影，像游戏菜单面板一样稳定清晰。
+- 输入框保持方形轮廓，聚焦时使用蓝色内描边，不使用发光或柔和阴影。
+- 装饰元素可使用像素星星、方块、血条、排行榜条目等图形，但数量克制，避免削弱信息阅读。
+</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>像素艺术风</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>复古 8-bit 游戏视觉，硬边轮廓，高饱和像素配色，强调无圆角、粗边框和瞬时反馈，营造经典街机与独立游戏的怀旧感。</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Web, MiniProgram</t>
+        </is>
+      </c>
+      <c r="W110" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t># Theme Name: 像素艺术风
+# Vibe &amp; Description:
+复古 8-bit 游戏视觉，硬边轮廓，高饱和像素配色，强调无圆角、粗边框和瞬时反馈，营造经典街机与独立游戏的怀旧感。
+# Color
+- 使用经典 8-bit 调色板，避免渐变、透明度过渡和柔和色彩。
+- 背景与边框使用深色像素黑（#1A1C2C），基础背景使用亮白（#F4F4F4），强调色使用红（#FF004D）、绿（#00E436）、蓝（#29ADFF）、黄（#FFEC27）。整体色彩应直接、鲜明、高对比，像早期游戏界面一样清晰有力。
+# Font
+- 使用「寒蝉点阵体16px」作为标题字体。（https://resource-static.bj.bcebos.com/fonts-skill/ChillBitmap_16px.ttf）
+- 使用「阿里巴巴普惠体3.0」作为正文字体。（https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf）
+# Animation
+- 所有交互采用瞬时硬切，不使用缓动、渐变或透明度动画。触摸时元素向右下移动 1-2px，同时阴影缩短或消失，形成“按下实体按钮”的反馈。
+- Hover 或选中状态采用 Palette Swap，直接切换为另一种 8-bit 强调色，如红色按钮切换为蓝色，不保留中间过渡状态。
+# Layout
+- 页面结构清晰分块，使用粗边框和硬边阴影建立层级。卡片、按钮、输入框均保持方正外观，禁止圆角。
+- mobile app 中保持紧凑但有节奏的网格排布，模块间距明确，重点区域可使用黄色标题、红色行动按钮和蓝绿色状态点缀。
+# Elements
+- 按钮使用 `border-4`、`rounded-none` 和 `shadow-[4px_4px_0_#1a1c2c]`，点击时位移并取消阴影。
+- 卡片使用白底、深色粗边框和硬边阴影，像游戏菜单面板一样稳定清晰。
+- 输入框保持方形轮廓，聚焦时使用蓝色内描边，不使用发光或柔和阴影。
+- 装饰元素可使用像素星星、方块、血条、排行榜条目等图形，但数量克制，避免削弱信息阅读。</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>水彩画风</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>柔和渐变，纸张纹理，半透明色彩层层晕染，强调流动、诗意和艺术感，模拟水彩在纸面自然扩散的视觉体验。</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="W111" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Theme Name: 水彩画风
+# Vibe &amp; Description:
+柔和渐变，纸张纹理，半透明色彩层层晕染，强调流动、诗意和艺术感，模拟水彩在纸面自然扩散的视觉体验。
+# Color
+- 背景使用温暖纸张色 `#FAF8F5`，避免纯白过冷或纯黑过硬。
+- 主色使用沉静蓝 `#4A6FA5`，搭配低饱和水彩强调色：陶土橙 `#E8A87C`、湖水青 `#85CDCA`、玫瑰灰 `#C38D94`、暖棕 `#D4A373`。
+- 卡片和浮层使用半透明渐变，如 `from-white/70 to-[#4A6FA5]/10`，制造水彩叠色感。
+- 边框使用极淡蓝灰：`border-[#4A6FA5]/20`，禁止硬黑边框、纯黑背景和高对比硬分割。
+# Font
+- 使用「沐瑶软笔手写体」作为标题字体。（https://resource-static.bj.bcebos.com/fonts-skill/MuyaoSoftbrush_Regular.ttf）
+- 使用「资源圆体」作为正文字体。（https://resource-static.bj.bcebos.com/fonts-skill/ResourceHanRoundedCN-Regular.ttf）
+## 字体引入方式
+在 `app/_layout.tsx` 中加载字体
+```js
+import { useFonts } from 'expo-font';
+const [fontsLoaded] = useFonts({
+  'MuyaoSoftbrush-Regular': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/MuyaoSoftbrush_Regular.ttf' },
+  'ResourceHanRoundedCN-Regular': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/ResourceHanRoundedCN-Regular.ttf' },
+});
+```
+`tailwind.config.js` 添加 fontFamily 属性扩展字体
+```js
+{
+  fontFamily: {
+   'title-muyao': ['MuyaoSoftbrush-Regular', 'sans-serif'],
+   'body-resource-rounded': ['ResourceHanRoundedCN-Regular', 'sans-serif'],
+  }
+}
+```
+## 字体使用示例
+```jsx
+&lt;Text className="font-title-muyao text-3xl"&gt;&lt;/Text&gt;
+&lt;Text className="font-body-resource-rounded text-base"&gt;&lt;/Text&gt;
+```
+# Animation
+- 触摸时元素轻微放大，如 `scale(1.02)`，按下时轻微回缩，如 `scale(0.98)`，避免硬朗位移。
+- 元素出现时采用柔和淡入、轻微模糊散开或透明度叠加，像水彩颜料逐渐渗入纸面。
+- 过渡节奏保持缓慢自然，建议使用 `duration-400 ease-out`。
+# Layout
+- 页面保留充足留白，像画纸上自然展开的内容层次。
+- 卡片采用大圆角和柔化阴影，推荐 `rounded-2xl` 或 `rounded-3xl`，避免直角与强投影。
+- 内容层级通过字号、透明度、色彩深浅和留白建立，不依赖厚重分割线。
+# Elements
+- 背景叠加柔和水彩渐变色块，可使用低透明度、模糊和不规则位置营造颜料扩散感。
+- 按钮使用圆角胶囊形或大圆角矩形，搭配半透明底色和柔和阴影。
+- 卡片使用半透明渐变背景、细边框和轻阴影，保持边缘柔软。
+- 装饰元素可使用淡色水渍、纸张噪点、手绘线条或模糊色块，但整体保持克制、安静、通透。
+</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>水彩画风</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>柔和渐变，纸张纹理，半透明色彩层层晕染，强调流动、诗意和艺术感，模拟水彩在纸面自然扩散的视觉体验。</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Web, MiniProgram</t>
+        </is>
+      </c>
+      <c r="W112" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t># Theme Name: 水彩画风
+# Vibe &amp; Description:
+柔和渐变，纸张纹理，半透明色彩层层晕染，强调流动、诗意和艺术感，模拟水彩在纸面自然扩散的视觉体验。
+# Color
+- 背景使用温暖纸张色 `#FAF8F5`，避免纯白过冷或纯黑过硬。
+- 主色使用沉静蓝 `#4A6FA5`，搭配低饱和水彩强调色：陶土橙 `#E8A87C`、湖水青 `#85CDCA`、玫瑰灰 `#C38D94`、暖棕 `#D4A373`。
+- 卡片和浮层使用半透明渐变，如 `from-white/70 to-[#4A6FA5]/10`，制造水彩叠色感。
+- 边框使用极淡蓝灰：`border-[#4A6FA5]/20`，禁止硬黑边框、纯黑背景和高对比硬分割。
+# Font
+- 使用「沐瑶软笔手写体」作为标题字体。（https://resource-static.bj.bcebos.com/fonts-skill/MuyaoSoftbrush_Regular.ttf）
+- 使用「资源圆体」作为正文字体。（https://resource-static.bj.bcebos.com/fonts-skill/ResourceHanRoundedCN-Regular.ttf）
+# Animation
+- 触摸时元素轻微放大，如 `scale(1.02)`，按下时轻微回缩，如 `scale(0.98)`，避免硬朗位移。
+- 元素出现时采用柔和淡入、轻微模糊散开或透明度叠加，像水彩颜料逐渐渗入纸面。
+- 过渡节奏保持缓慢自然，建议使用 `duration-400 ease-out`。
+# Layout
+- 页面保留充足留白，像画纸上自然展开的内容层次。
+- 卡片采用大圆角和柔化阴影，推荐 `rounded-2xl` 或 `rounded-3xl`，避免直角与强投影。
+- 内容层级通过字号、透明度、色彩深浅和留白建立，不依赖厚重分割线。
+# Elements
+- 背景叠加柔和水彩渐变色块，可使用低透明度、模糊和不规则位置营造颜料扩散感。
+- 按钮使用圆角胶囊形或大圆角矩形，搭配半透明底色和柔和阴影。
+- 卡片使用半透明渐变背景、细边框和轻阴影，保持边缘柔软。
+- 装饰元素可使用淡色水渍、纸张噪点、手绘线条或模糊色块，但整体保持克制、安静、通透。</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>水墨意境</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>水墨留白，宣纸纹理，融合书法、远山、印章与晕染墨迹，营造宁静、深邃、诗意的东方美学氛围。</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="W113" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Theme Name: 水墨意境
+# Vibe &amp; Description:
+水墨留白，宣纸纹理，融合书法、远山、印章与晕染墨迹，营造宁静、深邃、诗意的东方美学氛围。
+# Color
+- 以宣纸白与墨色层次为主，严格避免霓虹色、高饱和色和纯黑大面积背景。
+- 背景使用宣纸白（#F8F5F0）、米色（#FAF0E6）或象牙白（#FFFFF0），文字使用焦墨（#1A1A1A）、浓墨（#333333）、淡墨（#666666）和清墨（#999999）。
+- 点缀色保持克制：朱红印章色（#C41E3A）用于印章与关键标记，青绿山水色（#2E8B57）用于极少量山水意象，金色（#D4AF37）仅用于高端装饰细节。
+# Font
+- 使用「阿里妈妈东方大楷」作为标题字体。（https://resource-static.bj.bcebos.com/fonts-skill/AlimamaDongFangDaKai-Regular.ttf）
+- 使用「思源宋体」作为副标题与导航字体，保持流畅端正的书写感。（https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-Regular.woff2）
+## 字体引入方式
+在 `app/_layout.tsx` 中加载字体
+```js
+import { useFonts } from 'expo-font';
+const [fontsLoaded] = useFonts({
+  'AlimamaDongFangDaKai-Regular': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/AlimamaDongFangDaKai-Regular.ttf' },
+  'SourceHanSerifCN-Regular': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-Regular.woff2' },
+});
+```
+`tailwind.config.js` 添加 fontFamily 属性扩展字体
+```js
+{
+  fontFamily: {
+    'title-dongfangdakai': ['AlimamaDongFangDaKai-Regular', 'serif'],
+    'body-serif': ['SourceHanSerifCN-Regular', 'serif'],
+  }
+}
+```
+## 字体使用示例
+```jsx
+&lt;Text className="font-title-dongfangdakai text-3xl"&gt;&lt;/Text&gt;
+&lt;Text className="font-body-serif text-base"&gt;&lt;/Text&gt;
+```
+# Animation
+- 触摸或长按时，元素产生轻微墨晕扩散，边缘柔化并伴随透明度变化，像墨色在宣纸上慢慢渗开。
+- 页面元素出现时采用“淡入 + 轻微上浮”或“云雾渐显”的过渡，时长控制在 300-500ms，保持含蓄、缓慢、诗意的节奏。
+# Layout
+- 页面保留大量留白，元素之间疏朗分布，避免拥挤和强几何秩序。
+- 构图可略微不对称，形成自然的山水画卷感；标题可偏大，正文克制，局部加入竖排装饰文字增强古典氛围。
+- mobile app 中采用单列为主，保留书法标题、宣纸背景与留白节奏，触摸区域不小于 44px。
+# Elements
+- 卡片与按钮使用柔和墨色边缘，避免硬边阴影，可通过模糊、半透明和不规则形状模拟毛笔笔触。
+- 印章作为重点视觉符号，使用朱红方形或圆形，小面积点缀标题、按钮或空白处。
+- 背景叠加轻微宣纸噪点纹理，并可加入抽象远山、竹梅兰菊线条或淡墨泼染作为装饰。
+- 分割线与装饰图形应呈现干笔、晕染或虚实相生的效果，避免现代工业图标与锐利几何边框。
+</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>水墨意境</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>水墨留白，宣纸纹理，融合书法、远山、印章与晕染墨迹，营造宁静、深邃、诗意的东方美学氛围。</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Web, MiniProgram</t>
+        </is>
+      </c>
+      <c r="W114" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t># Theme Name: 水墨意境
+# Vibe &amp; Description:
+水墨留白，宣纸纹理，融合书法、远山、印章与晕染墨迹，营造宁静、深邃、诗意的东方美学氛围。
+# Color
+- 以宣纸白与墨色层次为主，严格避免霓虹色、高饱和色和纯黑大面积背景。
+- 背景使用宣纸白（#F8F5F0）、米色（#FAF0E6）或象牙白（#FFFFF0），文字使用焦墨（#1A1A1A）、浓墨（#333333）、淡墨（#666666）和清墨（#999999）。
+- 点缀色保持克制：朱红印章色（#C41E3A）用于印章与关键标记，青绿山水色（#2E8B57）用于极少量山水意象，金色（#D4AF37）仅用于高端装饰细节。
+# Font
+- 使用「阿里妈妈东方大楷」作为标题字体。（https://resource-static.bj.bcebos.com/fonts-skill/AlimamaDongFangDaKai-Regular.ttf）
+- 使用「思源宋体」作为副标题与导航字体，保持流畅端正的书写感。（https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-Regular.woff2）
+# Animation
+- 触摸或长按时，元素产生轻微墨晕扩散，边缘柔化并伴随透明度变化，像墨色在宣纸上慢慢渗开。
+- 页面元素出现时采用“淡入 + 轻微上浮”或“云雾渐显”的过渡，时长控制在 300-500ms，保持含蓄、缓慢、诗意的节奏。
+# Layout
+- 页面保留大量留白，元素之间疏朗分布，避免拥挤和强几何秩序。
+- 构图可略微不对称，形成自然的山水画卷感；标题可偏大，正文克制，局部加入竖排装饰文字增强古典氛围。
+- mobile app 中采用单列为主，保留书法标题、宣纸背景与留白节奏，触摸区域不小于 44px。
+# Elements
+- 卡片与按钮使用柔和墨色边缘，避免硬边阴影，可通过模糊、半透明和不规则形状模拟毛笔笔触。
+- 印章作为重点视觉符号，使用朱红方形或圆形，小面积点缀标题、按钮或空白处。
+- 背景叠加轻微宣纸噪点纹理，并可加入抽象远山、竹梅兰菊线条或淡墨泼染作为装饰。
+- 分割线与装饰图形应呈现干笔、晕染或虚实相生的效果，避免现代工业图标与锐利几何边框。</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>珊瑚节拍</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>浅色音乐播放器风格，暖米白背景与纯白卡片营造治愈通透的氛围，珊瑚橙作为播放控件强调色，整体柔和、现代、轻盈且富有节奏感。</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="W115" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Theme Name: 珊瑚节拍
+# Vibe &amp; Description:
+浅色音乐播放器风格，暖米白背景与纯白卡片营造治愈通透的氛围，珊瑚橙作为播放控件强调色，整体柔和、现代、轻盈且富有节奏感。
+# Color
+- 使用暖调浅色系统，避免深色背景和高饱和霓虹色。
+- 背景使用暖米白（#F8F6F2），卡片、菜单和底部播放栏使用纯白（#FFFFFF），文字使用深灰黑（#1C1C1E），辅助文字使用柔和灰（#6C6C70）。
+- 强调色使用珊瑚橙（#F97316），主要用于播放按钮、进度条状态和关键交互反馈。分割线使用浅灰（#EBEBEB / #EFEFEF），保持界面干净轻盈。
+# Font
+- 标题「优设标题黑」歌曲名使用中等加粗字重，营造清晰但不厚重的音乐卡片层级。（https://resource-static.bj.bcebos.com/fonts-skill/YouSheBiaoTiHei_Regular.ttf）
+- 正文「资源圆体」菜单项保持常规字重，辅助信息如艺术家、时长使用更轻的灰色小字号。（https://resource-static.bj.bcebos.com/fonts-skill/ResourceHanRoundedCN-Regular.ttf）
+## 字体引入方式
+在 `app/_layout.tsx` 中加载字体
+```js
+import { useFonts } from 'expo-font';
+const [fontsLoaded] = useFonts({
+  'YouSheBiaoTiHei-Regular': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/YouSheBiaoTiHei_Regular.ttf' },
+  'ResourceHanRoundedCN-Regular': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/ResourceHanRoundedCN-Regular.ttf' },
+});
+```
+`tailwind.config.js` 添加 fontFamily 属性扩展字体
+```js
+{
+  fontFamily: {
+    'title-youshe': ['YouSheBiaoTiHei-Regular', 'sans-serif'],
+    'body-resource-rounded': ['ResourceHanRoundedCN-Regular', 'sans-serif'],
+  }
+}
+```
+## 字体使用示例
+```jsx
+&lt;Text className="font-title-youshe text-3xl"&gt;&lt;/Text&gt;
+&lt;Text className="font-body-resource-rounded text-base"&gt;&lt;/Text&gt;
+```
+# Animation
+- 卡片触摸时轻微上浮并加深阴影，模拟歌单被选中的轻盈反馈。
+- 播放按钮点击或悬停时放大至 1.05 倍，强调音乐控制的即时感。
+- 菜单项切换使用短过渡，高亮背景从透明变为浅灰圆角块，保持柔和自然。
+- 进度条触摸时颜色由浅灰变亮，表现可交互状态，但不需要真实音频拖拽。
+# Layout
+- mobile app 采用单列主内容布局，整体背景为暖米白，内容区保持 16px 左右内边距。
+- 顶部显示问候语与轻量状态入口，下方放置“正在播放”迷你卡片，包含封面、歌曲名、艺术家、简易进度条和播放控制。
+- 推荐歌单使用单列卡片流，每张卡片包含浅色渐变封面占位、标题与艺术家信息。
+- 最近播放列表采用紧凑行布局，显示序号、歌曲名、艺术家和时长，行间使用浅灰分隔线。
+- 底部固定播放栏高度约 80px，包含当前歌曲缩略图、歌曲信息、播放按钮和简化进度状态。
+# Elements
+- 卡片统一使用纯白背景、16px 圆角、轻阴影，避免厚重阴影和过大的圆角。
+- 封面占位可使用柔和浅色渐变与音乐图标，作为唯一允许的轻微渐变元素。
+- 播放按钮使用珊瑚橙圆形或强调态样式，上一首、下一首保持深灰线性图标。
+- 菜单高亮使用浅灰圆角背景，不使用强烈色块。
+- 底部播放栏使用纯白背景与顶部浅灰分割线，形成稳定的播放器锚点。
+</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>珊瑚节拍</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>浅色音乐播放器风格，暖米白背景与纯白卡片营造治愈通透的氛围，珊瑚橙作为播放控件强调色，整体柔和、现代、轻盈且富有节奏感。</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Web, MiniProgram</t>
+        </is>
+      </c>
+      <c r="W116" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t># Theme Name: 珊瑚节拍
+# Vibe &amp; Description:
+浅色音乐播放器风格，暖米白背景与纯白卡片营造治愈通透的氛围，珊瑚橙作为播放控件强调色，整体柔和、现代、轻盈且富有节奏感。
+# Color
+- 使用暖调浅色系统，避免深色背景和高饱和霓虹色。
+- 背景使用暖米白（#F8F6F2），卡片、菜单和底部播放栏使用纯白（#FFFFFF），文字使用深灰黑（#1C1C1E），辅助文字使用柔和灰（#6C6C70）。
+- 强调色使用珊瑚橙（#F97316），主要用于播放按钮、进度条状态和关键交互反馈。分割线使用浅灰（#EBEBEB / #EFEFEF），保持界面干净轻盈。
+# Font
+- 标题「优设标题黑」歌曲名使用中等加粗字重，营造清晰但不厚重的音乐卡片层级。（https://resource-static.bj.bcebos.com/fonts-skill/YouSheBiaoTiHei_Regular.ttf）
+- 正文「资源圆体」菜单项保持常规字重，辅助信息如艺术家、时长使用更轻的灰色小字号。（https://resource-static.bj.bcebos.com/fonts-skill/ResourceHanRoundedCN-Regular.ttf）
+# Animation
+- 卡片触摸时轻微上浮并加深阴影，模拟歌单被选中的轻盈反馈。
+- 播放按钮点击或悬停时放大至 1.05 倍，强调音乐控制的即时感。
+- 菜单项切换使用短过渡，高亮背景从透明变为浅灰圆角块，保持柔和自然。
+- 进度条触摸时颜色由浅灰变亮，表现可交互状态，但不需要真实音频拖拽。
+# Layout
+- mobile app 采用单列主内容布局，整体背景为暖米白，内容区保持 16px 左右内边距。
+- 顶部显示问候语与轻量状态入口，下方放置“正在播放”迷你卡片，包含封面、歌曲名、艺术家、简易进度条和播放控制。
+- 推荐歌单使用单列卡片流，每张卡片包含浅色渐变封面占位、标题与艺术家信息。
+- 最近播放列表采用紧凑行布局，显示序号、歌曲名、艺术家和时长，行间使用浅灰分隔线。
+- 底部固定播放栏高度约 80px，包含当前歌曲缩略图、歌曲信息、播放按钮和简化进度状态。
+# Elements
+- 卡片统一使用纯白背景、16px 圆角、轻阴影，避免厚重阴影和过大的圆角。
+- 封面占位可使用柔和浅色渐变与音乐图标，作为唯一允许的轻微渐变元素。
+- 播放按钮使用珊瑚橙圆形或强调态样式，上一首、下一首保持深灰线性图标。
+- 菜单高亮使用浅灰圆角背景，不使用强烈色块。
+- 底部播放栏使用纯白背景与顶部浅灰分割线，形成稳定的播放器锚点。</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>故障画布</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>赛博朋克故障艺术，黑底霓虹，高科技低生活的反乌托邦氛围。以扫描线、色差偏移、斜切棱角和终端代码感构成危险、叛逆、机械化的视觉语言。</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="W117" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Theme Name: 故障画布
+# Vibe &amp; Description:
+赛博朋克故障艺术，黑底霓虹，高科技低生活的反乌托邦氛围。以扫描线、色差偏移、斜切棱角和终端代码感构成危险、叛逆、机械化的视觉语言。
+# Color
+- 使用极黑带紫作为主背景，避免任何浅色模式。背景色为 #0A0A0F，卡片色为 #12121A，边框色为 #2A2A3A。
+- 高亮色以霓虹绿 #00FF88 为主，用于按钮、光标、重点边框；洋红 #FF00FF 和青蓝 #00D4FF 用于故障偏移、辅助光效和扫描纹理。正文使用 #E0E0E0，次级文字使用 #6B7280，危险提示使用 #FF3366。
+# Font
+- 使用「未来荧黑」作为标题字体，保持机械、未来、宽字距的视觉感。（https://resource-static.bj.bcebos.com/fonts-skill/GlowSansSC-Normal-Bold.woff2）
+- 使用「阿里巴巴普惠体3.0」作为正文、终端和标签字体，强化代码界面与黑客终端氛围。（https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf）
+## 字体引入方式
+在 `app/_layout.tsx` 中加载字体
+```js
+import { useFonts } from 'expo-font';
+const [fontsLoaded] = useFonts({
+  'GlowSansSC-Normal-Bold': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/GlowSansSC-Normal-Bold.woff2' },
+  'AlibabaPuHuiTi-Regular': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf' },
+});
+```
+`tailwind.config.js` 添加 fontFamily 属性扩展字体
+```js
+{
+  fontFamily: {
+    'title-future': ['GlowSansSC-Normal-Bold', 'sans-serif'],
+    'body-alibaba': ['AlibabaPuHuiTi-Regular', 'sans-serif'],
+  }
+}
+```
+## 字体使用示例
+```jsx
+&lt;Text className="font-title-future text-3xl"&gt;&lt;/Text&gt;
+&lt;Text className="font-body-alibaba text-base"&gt;&lt;/Text&gt;
+```
+# Animation
+- 触摸时触发短促机械反馈：轻微位移、闪烁、霓虹发光增强，避免柔和缓动，使用 linear 或 step 节奏。
+- 标题与重点文字可加入红蓝色差偏移和轻微故障抖动；终端区域使用光标闪烁、扫描线流动和打字感出现效果。
+# Layout
+- 页面采用深色全屏背景，叠加扫描线、噪点和电路纹理。内容遵循 8px 间距网格，卡片可使用不对称排列，制造被切割和错位的未来界面感。
+- 移动端保持单列优先，触控目标不小于 44px。减少过强光晕，但保留黑底、霓虹、终端和故障纹理的核心识别度。
+# Elements
+- 按钮和卡片禁止圆角，使用直角、斜切角或 SVG / Skia 裁切形状，边框以霓虹绿或暗紫灰描边。
+- 标题使用 RGB 色差阴影，卡片使用霓虹 box-shadow，分割线采用扫描线或电路线条。
+- 至少保留一处终端命令行模块，包含 `$`、`&gt;_`、绿色代码文本和闪烁光标。
+- 背景叠加 repeating-linear-gradient 扫描纹理，局部加入洋红与青蓝光晕，形成老旧显示器故障质感。
+</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>故障画布</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>赛博朋克故障艺术，黑底霓虹，高科技低生活的反乌托邦氛围。以扫描线、色差偏移、斜切棱角和终端代码感构成危险、叛逆、机械化的视觉语言。</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Web, MiniProgram</t>
+        </is>
+      </c>
+      <c r="W118" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t># Theme Name: 故障画布
+# Vibe &amp; Description:
+赛博朋克故障艺术，黑底霓虹，高科技低生活的反乌托邦氛围。以扫描线、色差偏移、斜切棱角和终端代码感构成危险、叛逆、机械化的视觉语言。
+# Color
+- 使用极黑带紫作为主背景，避免任何浅色模式。背景色为 #0A0A0F，卡片色为 #12121A，边框色为 #2A2A3A。
+- 高亮色以霓虹绿 #00FF88 为主，用于按钮、光标、重点边框；洋红 #FF00FF 和青蓝 #00D4FF 用于故障偏移、辅助光效和扫描纹理。正文使用 #E0E0E0，次级文字使用 #6B7280，危险提示使用 #FF3366。
+# Font
+- 使用「未来荧黑」作为标题字体，保持机械、未来、宽字距的视觉感。（https://resource-static.bj.bcebos.com/fonts-skill/GlowSansSC-Normal-Bold.woff2）
+- 使用「阿里巴巴普惠体3.0」作为正文、终端和标签字体，强化代码界面与黑客终端氛围。（https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf）
+# Animation
+- 触摸时触发短促机械反馈：轻微位移、闪烁、霓虹发光增强，避免柔和缓动，使用 linear 或 step 节奏。
+- 标题与重点文字可加入红蓝色差偏移和轻微故障抖动；终端区域使用光标闪烁、扫描线流动和打字感出现效果。
+# Layout
+- 页面采用深色全屏背景，叠加扫描线、噪点和电路纹理。内容遵循 8px 间距网格，卡片可使用不对称排列，制造被切割和错位的未来界面感。
+- 移动端保持单列优先，触控目标不小于 44px。减少过强光晕，但保留黑底、霓虹、终端和故障纹理的核心识别度。
+# Elements
+- 按钮和卡片禁止圆角，使用直角、斜切角或 SVG / Skia 裁切形状，边框以霓虹绿或暗紫灰描边。
+- 标题使用 RGB 色差阴影，卡片使用霓虹 box-shadow，分割线采用扫描线或电路线条。
+- 至少保留一处终端命令行模块，包含 `$`、`&gt;_`、绿色代码文本和闪烁光标。
+- 背景叠加 repeating-linear-gradient 扫描纹理，局部加入洋红与青蓝光晕，形成老旧显示器故障质感。</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>粉黑画廊</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>极深黑背景，高饱和粉色强调，极简杂志式画廊布局，冷静锋利的艺术刊物气质。</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="W119" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t># Theme Name: 粉黑画廊
+# Vibe &amp; Description:
+极深黑背景，高饱和粉色强调，极简杂志式画廊布局，冷静锋利的艺术刊物气质。
+# Color
+- 使用极深黑作为主背景，搭配深灰黑卡片与高饱和粉色强调色。
+- 背景使用 #121212，卡片使用 #1C1C1C，文字以高对比白色与浅灰为主。强调色使用 HSL(340, 80%, 62%)，用于按钮、选中状态、光晕、标签和关键交互反馈，形成强烈但克制的视觉冲击。
+# Font
+- 标题使用：HarmonyOS Sans字体（https://resource-static.bj.bcebos.com/fonts-skill/HarmonyOSSans_Bold.ttf）
+- 正文：HarmonyOS Sans字体（https://resource-static.bj.bcebos.com/fonts-skill/HarmonyOSSans_Regular.ttf）
+## 字体引入方式
+在 `app/_layout.tsx` 中使用系统字体，无需额外加载字体文件。
+```js
+import { useFonts } from 'expo-font';
+const [fontsLoaded] = useFonts({
+  'HarmonyOSSans-Bold': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/HarmonyOSSans_Bold.ttf' },
+  'HarmonyOSSans-Regular': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/HarmonyOSSans_Regular.ttf' },
+});
+```
+`tailwind.config.js` 可保留默认 fontFamily，或扩展系统字体族。
+```js
+{
+  fontFamily: {
+   'harmony-title': ['HarmonyOSSans-Bold', 'sans-serif'],
+    'harmony-body': ['HarmonyOSSans-Regular', 'sans-serif'],
+  }
+}
+```
+## 字体使用示例
+```jsx
+&lt;Text className="font-harmony-title text-3xl"&gt;&lt;/Text&gt;
+&lt;Text className="font-harmony-body text-base"&gt;&lt;/Text&gt;
+```
+# Animation
+- 卡片触摸时轻微上浮，阴影加深，形成精致的画廊悬停感。按钮点击时使用短促的透明度或缩放反馈，避免夸张动效。
+- 图片打开时采用暗色遮罩与轻微缩放弹入效果，模拟作品被置于聚光灯下的沉浸式预览。模式切换、布局切换和内容出现保持 0.2-0.25s 的柔和过渡。
+# Layout
+- 移动端采用单列或双列作品流布局，卡片之间保持充足间距，整体宽松、克制，像一本深色艺术作品集。
+- 首页突出大标题、简短说明和主操作按钮，作品区支持网格、杂志感错位和瀑布流式排布。编辑控件仅在需要时出现，不遮挡作品主体。
+# Elements
+- 卡片使用 12px 圆角，图片使用 8px 圆角，按钮使用胶囊形圆角，整体边缘柔和但不过度圆润。
+- 作品图片支持点击放大，背景变暗，关闭按钮与操作控件使用粉色强调。
+- 标签、布局切换按钮和编辑入口采用细小高亮，保持功能清晰但不破坏画廊氛围。
+- 禁止厚重阴影、复杂纹理、大面积渐变和固定宽度布局，保持极简、响应式和高对比度。</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>粉黑画廊</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>极深黑背景，高饱和粉色强调，极简杂志式画廊布局，冷静锋利的艺术刊物气质。</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Web, MiniProgram</t>
+        </is>
+      </c>
+      <c r="W120" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t># Theme Name: 粉黑画廊
+# Vibe &amp; Description:
+极深黑背景，高饱和粉色强调，极简杂志式画廊布局，冷静锋利的艺术刊物气质。
+# Color
+- 使用极深黑作为主背景，搭配深灰黑卡片与高饱和粉色强调色。
+- 背景使用 #121212，卡片使用 #1C1C1C，文字以高对比白色与浅灰为主。强调色使用 HSL(340, 80%, 62%)，用于按钮、选中状态、光晕、标签和关键交互反馈，形成强烈但克制的视觉冲击。
+# Font
+- 标题使用：HarmonyOS Sans字体（https://resource-static.bj.bcebos.com/fonts-skill/HarmonyOSSans_Bold.ttf）
+- 正文：HarmonyOS Sans字体（https://resource-static.bj.bcebos.com/fonts-skill/HarmonyOSSans_Regular.ttf）
+# Animation
+- 卡片触摸时轻微上浮，阴影加深，形成精致的画廊悬停感。按钮点击时使用短促的透明度或缩放反馈，避免夸张动效。
+- 图片打开时采用暗色遮罩与轻微缩放弹入效果，模拟作品被置于聚光灯下的沉浸式预览。模式切换、布局切换和内容出现保持 0.2-0.25s 的柔和过渡。
+# Layout
+- 移动端采用单列或双列作品流布局，卡片之间保持充足间距，整体宽松、克制，像一本深色艺术作品集。
+- 首页突出大标题、简短说明和主操作按钮，作品区支持网格、杂志感错位和瀑布流式排布。编辑控件仅在需要时出现，不遮挡作品主体。
+# Elements
+- 卡片使用 12px 圆角，图片使用 8px 圆角，按钮使用胶囊形圆角，整体边缘柔和但不过度圆润。
+- 作品图片支持点击放大，背景变暗，关闭按钮与操作控件使用粉色强调。
+- 标签、布局切换按钮和编辑入口采用细小高亮，保持功能清晰但不破坏画廊氛围。
+- 禁止厚重阴影、复杂纹理、大面积渐变和固定宽度布局，保持极简、响应式和高对比度。</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>侘寂绿意</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>东方极简，侘寂留白，自然材质感，采用深竹绿与暖白调色，强调植物的生命力、手作温度和安静的生活气息。</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="W121" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Theme Name: 侘寂绿意
+# Vibe &amp; Description:
+东方极简，侘寂留白，自然材质感，采用深竹绿与暖白调色，强调植物的生命力、手作温度和安静的生活气息。
+# Color
+- 以暖白（#FAFAF7）作为大面积背景，营造自然留白与柔和纸感。
+- 深竹绿（#2D5016）作为主色，用于导航、按钮、价格和关键操作。
+- 炭灰（#2C2C2C）用于正文与说明文字，保持清晰但不生硬。
+- 淡金（#C9A84C）仅作为少量点缀，用于标签、细线、价格强调或装饰金线。
+- 深色区域可使用浅竹绿（#1E3A0F），搭配暖白文字，形成沉静的品牌段落。
+# Font
+- 使用「思源宋体」作为品牌标题、页面标题和重要数字字体。（https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-SemiBold.woff2）
+- 使用「思源宋体」作为正文、导航、按钮和说明文字字体。（https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-Regular.woff2）
+## 字体引入方式
+在 `app/_layout.tsx` 中加载字体
+```js
+import { useFonts } from 'expo-font';
+const [fontsLoaded] = useFonts({
+  'SourceHanSerifCN-SemiBold': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-SemiBold.woff2' },
+  'SourceHanSerifCN-Regular': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-Regular.woff2' },
+});
+```
+`tailwind.config.js` 添加 fontFamily 属性扩展字体
+```js
+{
+  fontFamily: {
+    'source-serif-title': ['SourceHanSerifCN-SemiBold', 'serif'],
+    'source-serif-body': ['SourceHanSerifCN-Regular', 'serif'],
+  }
+}
+```
+## 字体使用示例
+```jsx
+&lt;Text className="font-source-serif-title text-3xl"&gt;&lt;/Text&gt;
+&lt;Text className="font-source-serif-body text-base"&gt;&lt;/Text&gt;
+```
+# Animation
+- 点击按钮时使用 160ms 的轻微按压反馈，保持克制、快速、自然。
+- 卡片、商品和图文区域出现时采用“淡入 + 上移”的入场动画，延迟依次递进，营造安静的仪式感。
+- 悬停或触摸时，卡片轻微上浮 2px，边框或阴影柔和增强，避免夸张动效。
+- 尊重 `prefers-reduced-motion`，减少动效时关闭过渡和入场动画。
+# Layout
+- 页面以纵向滚动为主，保持充足留白和清晰分段。
+- 内容与图片采用不完全对称的构图关系，模拟 60% 信息与 40% 视觉的平衡感。
+- 间距遵循 4px 网格，段落呼吸感充足，标题行高紧凑，正文行高舒展。
+- 商品卡片、品牌介绍、购物车区域使用柔和分组，避免密集堆叠。
+# Elements
+- 按钮使用 8px 圆角，卡片使用 12px-16px 圆角，避免完全圆形的过度可爱感。
+- 标签使用淡金底色与小圆角，表现“热销”“新品”等轻量信息。
+- 边框使用半透明深竹绿或炭灰，卡片默认无重阴影，保持扁平与安静。
+- 分割线可使用竹节渐变线或 1px 淡金细线，作为细腻的东方装饰。
+- 图片选择低饱和植物摄影，强调自然纹理、泥土、叶片和光影，不使用杂乱背景。
+</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>侘寂绿意</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>东方极简，侘寂留白，自然材质感，采用深竹绿与暖白调色，强调植物的生命力、手作温度和安静的生活气息。</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Web, MiniProgram</t>
+        </is>
+      </c>
+      <c r="W122" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t># Theme Name: 侘寂绿意
+# Vibe &amp; Description:
+东方极简，侘寂留白，自然材质感，采用深竹绿与暖白调色，强调植物的生命力、手作温度和安静的生活气息。
+# Color
+- 以暖白（#FAFAF7）作为大面积背景，营造自然留白与柔和纸感。
+- 深竹绿（#2D5016）作为主色，用于导航、按钮、价格和关键操作。
+- 炭灰（#2C2C2C）用于正文与说明文字，保持清晰但不生硬。
+- 淡金（#C9A84C）仅作为少量点缀，用于标签、细线、价格强调或装饰金线。
+- 深色区域可使用浅竹绿（#1E3A0F），搭配暖白文字，形成沉静的品牌段落。
+# Font
+- 使用「思源宋体」作为品牌标题、页面标题和重要数字字体。（https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-SemiBold.woff2）
+- 使用「思源宋体」作为正文、导航、按钮和说明文字字体。（https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-Regular.woff2）
+# Animation
+- 点击按钮时使用 160ms 的轻微按压反馈，保持克制、快速、自然。
+- 卡片、商品和图文区域出现时采用“淡入 + 上移”的入场动画，延迟依次递进，营造安静的仪式感。
+- 悬停或触摸时，卡片轻微上浮 2px，边框或阴影柔和增强，避免夸张动效。
+- 尊重 `prefers-reduced-motion`，减少动效时关闭过渡和入场动画。
+# Layout
+- 页面以纵向滚动为主，保持充足留白和清晰分段。
+- 内容与图片采用不完全对称的构图关系，模拟 60% 信息与 40% 视觉的平衡感。
+- 间距遵循 4px 网格，段落呼吸感充足，标题行高紧凑，正文行高舒展。
+- 商品卡片、品牌介绍、购物车区域使用柔和分组，避免密集堆叠。
+# Elements
+- 按钮使用 8px 圆角，卡片使用 12px-16px 圆角，避免完全圆形的过度可爱感。
+- 标签使用淡金底色与小圆角，表现“热销”“新品”等轻量信息。
+- 边框使用半透明深竹绿或炭灰，卡片默认无重阴影，保持扁平与安静。
+- 分割线可使用竹节渐变线或 1px 淡金细线，作为细腻的东方装饰。
+- 图片选择低饱和植物摄影，强调自然纹理、泥土、叶片和光影，不使用杂乱背景。</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>赛璐璐动画风</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>粗黑轮廓，平面色块，高饱和配色，硬质阴影，模拟传统赛璐璐动画与卡通游戏菜单的视觉感。</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="W123" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Theme Name: 赛璐璐动画风
+# Vibe &amp; Description:
+粗黑轮廓，平面色块，高饱和配色，硬质阴影，模拟传统赛璐璐动画与卡通游戏菜单的视觉感。
+# Color
+- 使用高饱和、强对比的纯色系统，禁止渐变、柔和灰调和低饱和配色。
+- 背景与边框以深墨色（#1A1A2E）建立清晰轮廓，浅色区域使用暖白（#FAFAF5）。强调色使用动画感强烈的红（#E63946）、蓝（#4EA8DE）、绿（#2ECC71）和黄（#F1C40F）。整体色彩应像手绘动画分层上色，明快、直接、有游戏感。
+# Font
+- 标题使用 优设标题黑字体，使用粗重、紧凑、醒目的标题字体，强调 uppercase、font-black 和强视觉冲击。（https://resource-static.bj.bcebos.com/fonts-skill/YouSheBiaoTiHei_Regular.ttf）
+- 正文使用 阿里巴巴普惠体3.0 字体，（https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf）
+## 字体引入方式
+在 `app/_layout.tsx` 中加载字体
+```js
+import { useFonts } from 'expo-font';
+const [fontsLoaded] = useFonts({
+  'YouSheBiaoTiHei-Regular': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/YouSheBiaoTiHei_Regular.ttf' },
+  'AlibabaPuHuiTi-Regular': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf' },
+});
+```
+`tailwind.config.js` 添加 fontFamily 属性扩展字体
+```js
+{
+  fontFamily: {
+   'youshe-title': ['YouSheBiaoTiHei-Regular', 'sans-serif'],
+    'alibaba-puhuiti-body': ['AlibabaPuHuiTi-Regular', 'sans-serif'],
+  }
+}
+```
+## 字体使用示例
+```jsx
+&lt;Text className="font-youshe-title text-3xl"&gt;&lt;/Text&gt;
+&lt;Text className="font-alibaba-puhuiti-body text-base"&gt;&lt;/Text&gt;
+```
+# Animation
+- 交互节奏短促直接，时长控制在 75-150ms，模拟动画抽帧而不是丝滑过渡。
+- 点击时使用轻微位移、硬阴影缩小和 Squash &amp; Stretch 挤压反馈，例如 `scale-x-110 scale-y-90`，让按钮像卡通道具一样被按下。
+# Layout
+- 页面使用直角切割、粗黑分隔和明确对齐，所有元素像动画分镜中的独立色块。
+- 卡片、按钮和信息区保持稳定尺寸，移动端触控目标不低于 44px，整体布局可以略有不对称，但必须保持清晰层级。
+# Elements
+- 按钮和卡片统一使用 `border-[3px] border-[#1a1a2e] rounded-none`，形成强烈赛璐璐描边。
+- 阴影使用无模糊硬偏移，例如 `shadow-[3px_3px_0_#1a1a2e]`，禁止柔和投影。
+- 元素填充使用纯色块，不使用渐变；红、蓝、绿、黄可作为主要操作和状态色。
+</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>赛璐璐动画风</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>粗黑轮廓，平面色块，高饱和配色，硬质阴影，模拟传统赛璐璐动画与卡通游戏菜单的视觉感。</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Web, MiniProgram</t>
+        </is>
+      </c>
+      <c r="W124" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t># Theme Name: 赛璐璐动画风
+# Vibe &amp; Description:
+粗黑轮廓，平面色块，高饱和配色，硬质阴影，模拟传统赛璐璐动画与卡通游戏菜单的视觉感。
+# Color
+- 使用高饱和、强对比的纯色系统，禁止渐变、柔和灰调和低饱和配色。
+- 背景与边框以深墨色（#1A1A2E）建立清晰轮廓，浅色区域使用暖白（#FAFAF5）。强调色使用动画感强烈的红（#E63946）、蓝（#4EA8DE）、绿（#2ECC71）和黄（#F1C40F）。整体色彩应像手绘动画分层上色，明快、直接、有游戏感。
+# Font
+- 标题使用 优设标题黑字体，使用粗重、紧凑、醒目的标题字体，强调 uppercase、font-black 和强视觉冲击。（https://resource-static.bj.bcebos.com/fonts-skill/YouSheBiaoTiHei_Regular.ttf）
+- 正文使用 阿里巴巴普惠体3.0 字体，（https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf）
+# Animation
+- 交互节奏短促直接，时长控制在 75-150ms，模拟动画抽帧而不是丝滑过渡。
+- 点击时使用轻微位移、硬阴影缩小和 Squash &amp; Stretch 挤压反馈，例如 `scale-x-110 scale-y-90`，让按钮像卡通道具一样被按下。
+# Layout
+- 页面使用直角切割、粗黑分隔和明确对齐，所有元素像动画分镜中的独立色块。
+- 卡片、按钮和信息区保持稳定尺寸，移动端触控目标不低于 44px，整体布局可以略有不对称，但必须保持清晰层级。
+# Elements
+- 按钮和卡片统一使用 `border-[3px] border-[#1a1a2e] rounded-none`，形成强烈赛璐璐描边。
+- 阴影使用无模糊硬偏移，例如 `shadow-[3px_3px_0_#1a1a2e]`，禁止柔和投影。
+- 元素填充使用纯色块，不使用渐变；红、蓝、绿、黄可作为主要操作和状态色。</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>哥特式风格</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>中世纪大教堂美学，深紫、血红与黑色构成暗色基调，搭配金色装饰线条、尖拱轮廓和玫瑰窗纹样，营造黑暗、庄严、神秘的古典氛围。</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="W125" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Theme Name: 哥特式风格
+# Vibe &amp; Description:
+中世纪大教堂美学，深紫、血红与黑色构成暗色基调，搭配金色装饰线条、尖拱轮廓和玫瑰窗纹样，营造黑暗、庄严、神秘的古典氛围。
+# Color
+- 严格使用深紫、血红、黑色与金色，避免纯白、浅灰、粉色、绿色、蓝色和霓虹色。
+- 背景以黑色（#000000）或深紫（#2D1B4E）为主，局部使用血红（#8B0000）制造宗教壁画般的厚重感。文字与装饰使用金色（#FFD700 / #c9a227），边框使用半透明金色（border-[#c9a227]/40），整体呈现“暗夜大教堂”的肃穆视觉。
+# Font
+- 使用「思源宋体」作为标题字体。（https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-Bold.woff2）
+- 使用「阿里巴巴普惠体3.0」作为正文字体。（https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf）
+## 字体引入方式
+在 `app/_layout.tsx` 中加载字体
+```js
+import { useFonts } from 'expo-font';
+const [fontsLoaded] = useFonts({
+  'SourceHanSerifCN-Bold': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-Bold.woff2' },
+  'AlibabaPuHuiTi-Regular': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf' },
+});
+```
+`tailwind.config.js` 添加 fontFamily 属性扩展字体
+```js
+{
+  fontFamily: {
+    'title-serif-bold': ['SourceHanSerifCN-Bold', 'serif'],
+    'body-alibaba': ['AlibabaPuHuiTi-Regular', 'sans-serif'],
+  }
+}
+```
+## 字体使用示例
+```jsx
+&lt;Text className="font-title-serif-bold text-3xl"&gt;&lt;/Text&gt;
+&lt;Text className="font-body-alibaba text-base"&gt;&lt;/Text&gt;
+```
+# Animation
+- 触摸时不做轻快弹跳，使用金色光晕与阴影加深作为反馈，保持庄严克制。点击时可轻微缩放至 `active:scale-95`。
+- 元素出现时采用缓慢淡入或暗部浮现效果，像烛光照亮石雕纹样。过渡统一使用 `transition-all duration-300 ease-in-out`。
+# Layout
+- 页面以垂直、对称、仪式感强的结构为主，模拟教堂中轴线。移动端保持单列布局，卡片和区块之间留出充足呼吸感。
+- 区块边缘可加入尖拱、金色细线或手抄本式边框。卡片使用直角造型，避免圆润轮廓，整体层级通过暗色深浅、金色描边和字号差异建立。
+# Elements
+- 按钮使用透明底、金色描边和衬线文字，悬停或按压时出现半透明金色背景与暗色文字。
+- 卡片使用 `bg-[#0a0a0a]/90`、`border-2 border-[#c9a227]/40`、`rounded-none`，阴影采用深色扩散或金色光晕。
+- 装饰元素优先使用尖拱形、玫瑰窗、飞扶壁线条和手抄本边框，强化中世纪哥特氛围。
+- 分割线、图标和导航强调金色细线感，避免现代圆角、柔和卡通形态和高饱和亮色。
+</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>哥特式风格</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>中世纪大教堂美学，深紫、血红与黑色构成暗色基调，搭配金色装饰线条、尖拱轮廓和玫瑰窗纹样，营造黑暗、庄严、神秘的古典氛围。</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Web, MiniProgram</t>
+        </is>
+      </c>
+      <c r="W126" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t># Theme Name: 哥特式风格
+# Vibe &amp; Description:
+中世纪大教堂美学，深紫、血红与黑色构成暗色基调，搭配金色装饰线条、尖拱轮廓和玫瑰窗纹样，营造黑暗、庄严、神秘的古典氛围。
+# Color
+- 严格使用深紫、血红、黑色与金色，避免纯白、浅灰、粉色、绿色、蓝色和霓虹色。
+- 背景以黑色（#000000）或深紫（#2D1B4E）为主，局部使用血红（#8B0000）制造宗教壁画般的厚重感。文字与装饰使用金色（#FFD700 / #c9a227），边框使用半透明金色（border-[#c9a227]/40），整体呈现“暗夜大教堂”的肃穆视觉。
+# Font
+- 使用「思源宋体」作为标题字体。（https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-Bold.woff2）
+- 使用「阿里巴巴普惠体3.0」作为正文字体。（https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf）
+# Animation
+- 触摸时不做轻快弹跳，使用金色光晕与阴影加深作为反馈，保持庄严克制。点击时可轻微缩放至 `active:scale-95`。
+- 元素出现时采用缓慢淡入或暗部浮现效果，像烛光照亮石雕纹样。过渡统一使用 `transition-all duration-300 ease-in-out`。
+# Layout
+- 页面以垂直、对称、仪式感强的结构为主，模拟教堂中轴线。移动端保持单列布局，卡片和区块之间留出充足呼吸感。
+- 区块边缘可加入尖拱、金色细线或手抄本式边框。卡片使用直角造型，避免圆润轮廓，整体层级通过暗色深浅、金色描边和字号差异建立。
+# Elements
+- 按钮使用透明底、金色描边和衬线文字，悬停或按压时出现半透明金色背景与暗色文字。
+- 卡片使用 `bg-[#0a0a0a]/90`、`border-2 border-[#c9a227]/40`、`rounded-none`，阴影采用深色扩散或金色光晕。
+- 装饰元素优先使用尖拱形、玫瑰窗、飞扶壁线条和手抄本边框，强化中世纪哥特氛围。
+- 分割线、图标和导航强调金色细线感，避免现代圆角、柔和卡通形态和高饱和亮色。</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>欧普艺术</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>光学幻觉，黑白高对比，精密几何图案，强调视觉张力与平面运动感，以克制的振动色彩制造强烈记忆点。</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="W127" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Theme Name: 欧普艺术
+# Vibe &amp; Description:
+光学幻觉，黑白高对比，精密几何图案，强调视觉张力与平面运动感，以克制的振动色彩制造强烈记忆点。
+# Color
+- 以纯黑与纯白作为绝对主色，保持清晰、锐利、无灰度过渡的视觉对抗。
+- 背景与文字采用高反差组合：黑底白字或白底黑字。点缀色仅使用振动色彩对，如朱红（#FF3300）、亮蓝（#0066FF）、明黄（#FFCC00）和橄榄绿（#5E6D00）。禁止柔和渐变、半透明、模糊和低对比阴影。
+# Font
+- 使用「阿里巴巴普惠体3.0」作为标题字体，保持大写感、几何感和强节奏。（https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_SemiBold.ttf）
+- 使用「阿里巴巴普惠体3.0」作为正文字体，确保移动端阅读清晰。（https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf）
+## 字体引入方式
+在 `app/_layout.tsx` 中加载字体
+```js
+import { useFonts } from 'expo-font';
+const [fontsLoaded] = useFonts({
+  'AlibabaPuHuiTi-SemiBold': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_SemiBold.ttf' },
+  'AlibabaPuHuiTi-Regular': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf' },
+});
+```
+`tailwind.config.js` 添加 fontFamily 属性统一字体语义
+```js
+{
+  fontFamily: {
+    'alibaba-puhuiti-title': ['AlibabaPuHuiTi-SemiBold', 'sans-serif'],
+    'alibaba-puhuiti-body': ['AlibabaPuHuiTi-Regular', 'sans-serif'],
+  }
+}
+```
+## 字体使用示例
+```jsx
+&lt;Text className="font-alibaba-puhuiti-title text-3xl"&gt;&lt;/Text&gt;
+&lt;Text className="font-alibaba-puhuiti-body text-base"&gt;&lt;/Text&gt;
+```
+# Animation
+- 点击时使用硬朗的按压反馈，如轻微位移 `translate-x-[2px] translate-y-[2px]`，避免柔和弹性动画。
+- 交互状态以黑白反转、边框强调或硬边投影变化为主，过渡仅使用短促的颜色变化，保持机械、精确的节奏。
+# Layout
+- 页面以移动端单列为主，信息层级清晰，标题大、间距足、装饰克制。
+- 卡片、按钮和区块保持直角边框，使用 `border-2 border-black rounded-none`，可搭配 `4px` 硬边偏移阴影，形成海报式几何秩序。
+# Elements
+- 使用同心圆、棋盘格、条纹、莫尔纹作为局部装饰，不大面积铺满，避免造成视觉疲劳。
+- 按钮采用黑白反转样式，必要时用朱红或亮蓝作为边线、角标或小面积色块点缀。
+- 卡片使用纯白或纯黑底色，搭配清晰边框和无圆角结构，保持强烈平面感。
+- 所有视觉元素避免柔和阴影、圆角、渐变和玻璃拟态，整体呈现锐利、精密、光学化的移动端界面。
+</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>欧普艺术</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>光学幻觉，黑白高对比，精密几何图案，强调视觉张力与平面运动感，以克制的振动色彩制造强烈记忆点。</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Web, MiniProgram</t>
+        </is>
+      </c>
+      <c r="W128" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t># Theme Name: 欧普艺术
+# Vibe &amp; Description:
+光学幻觉，黑白高对比，精密几何图案，强调视觉张力与平面运动感，以克制的振动色彩制造强烈记忆点。
+# Color
+- 以纯黑与纯白作为绝对主色，保持清晰、锐利、无灰度过渡的视觉对抗。
+- 背景与文字采用高反差组合：黑底白字或白底黑字。点缀色仅使用振动色彩对，如朱红（#FF3300）、亮蓝（#0066FF）、明黄（#FFCC00）和橄榄绿（#5E6D00）。禁止柔和渐变、半透明、模糊和低对比阴影。
+# Font
+- 使用「阿里巴巴普惠体3.0」作为标题字体，保持大写感、几何感和强节奏。（https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_SemiBold.ttf）
+- 使用「阿里巴巴普惠体3.0」作为正文字体，确保移动端阅读清晰。（https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf）
+# Animation
+- 点击时使用硬朗的按压反馈，如轻微位移 `translate-x-[2px] translate-y-[2px]`，避免柔和弹性动画。
+- 交互状态以黑白反转、边框强调或硬边投影变化为主，过渡仅使用短促的颜色变化，保持机械、精确的节奏。
+# Layout
+- 页面以移动端单列为主，信息层级清晰，标题大、间距足、装饰克制。
+- 卡片、按钮和区块保持直角边框，使用 `border-2 border-black rounded-none`，可搭配 `4px` 硬边偏移阴影，形成海报式几何秩序。
+# Elements
+- 使用同心圆、棋盘格、条纹、莫尔纹作为局部装饰，不大面积铺满，避免造成视觉疲劳。
+- 按钮采用黑白反转样式，必要时用朱红或亮蓝作为边线、角标或小面积色块点缀。
+- 卡片使用纯白或纯黑底色，搭配清晰边框和无圆角结构，保持强烈平面感。
+- 所有视觉元素避免柔和阴影、圆角、渐变和玻璃拟态，整体呈现锐利、精密、光学化的移动端界面。</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>手绘风格</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>不规则线条，纸张纹理，带有涂鸦和便签感，强调真实、松弛、有人味的手绘草稿气质。</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="W129" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Theme Name: 手绘风格
+# Vibe &amp; Description:
+不规则线条，纸张纹理，带有涂鸦和便签感，强调真实、松弛、有人味的手绘草稿气质。
+# Color
+- 色彩保持克制，只使用暖纸白、铅笔黑、旧纸灰、修正红和圆珠笔蓝。
+- 背景使用暖纸色（#FDFBF7），文字使用柔和铅笔黑（#2D2D2D），避免纯黑带来的机械感。辅助灰使用旧纸色（#E5E0D8），强调色使用修正红（#FF4D4D），少量蓝色（#2D5DA1）作为手写标记或聚焦状态。
+# Font
+- 使用「沐瑶软笔手写体」作为标题字体，字重偏粗，像粗毡尖笔写出的标题。（https://resource-static.bj.bcebos.com/fonts-skill/MuyaoSoftbrush_Regular.ttf）
+- 使用「资源圆体」作为正文字体，保持清晰可读，同时保留手写感。（https://resource-static.bj.bcebos.com/fonts-skill/ResourceHanRoundedCN-Regular.ttf）
+## 字体引入方式
+在 `app/_layout.tsx` 中加载字体
+```js
+import { useFonts } from 'expo-font';
+const [fontsLoaded] = useFonts({
+  'MuyaoSoftbrush-Regular': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/MuyaoSoftbrush_Regular.ttf' },
+  'ResourceHanRoundedCN-Regular': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/ResourceHanRoundedCN-Regular.ttf' },
+});
+```
+`tailwind.config.js` 添加 fontFamily 属性扩展字体
+```js
+{
+  fontFamily: {
+   'title-muyao': ['MuyaoSoftbrush-Regular', 'sans-serif'],
+   'body-resource-rounded': ['ResourceHanRoundedCN-Regular', 'sans-serif'],
+  }
+}
+```
+## 字体使用示例
+```jsx
+&lt;Text className="font-title-muyao text-3xl"&gt;&lt;/Text&gt;
+&lt;Text className="font-body-resource-rounded text-base"&gt;&lt;/Text&gt;
+```
+# Animation
+- 触摸时元素产生轻微位移，阴影从 `4px 4px 0` 缩短到 `2px 2px 0`，形成纸片被按下的反馈。
+- 卡片或按钮悬停时可轻微旋转 1-2 度，动作快速直接，像手绘贴纸被轻轻拨动。
+# Layout
+- 页面像草稿本上的拼贴排版，允许轻微错位、重叠和不对称，不追求精确网格。
+- 卡片、图片和提示标签可带有小角度旋转，留白宽松，整体保持“随手整理过”的轻松秩序。
+# Elements
+- 所有按钮、卡片和输入框都使用不规则圆角，避免标准圆角，边框呈现手绘抖动感。
+- 边框使用较粗的铅笔黑实线，辅助分割线可使用虚线，阴影采用无模糊硬偏移效果。
+- 背景叠加淡淡纸张点阵纹理，例如 `radial-gradient(#E5E0D8 1px, transparent 1px)`。
+- 可使用胶带、图钉、虚线箭头、便签标签和涂鸦下划线作为装饰，但保持少量点缀。
+</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>手绘风格</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>不规则线条，纸张纹理，带有涂鸦和便签感，强调真实、松弛、有人味的手绘草稿气质。</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Web, MiniProgram</t>
+        </is>
+      </c>
+      <c r="W130" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t># Theme Name: 手绘风格
+# Vibe &amp; Description:
+不规则线条，纸张纹理，带有涂鸦和便签感，强调真实、松弛、有人味的手绘草稿气质。
+# Color
+- 色彩保持克制，只使用暖纸白、铅笔黑、旧纸灰、修正红和圆珠笔蓝。
+- 背景使用暖纸色（#FDFBF7），文字使用柔和铅笔黑（#2D2D2D），避免纯黑带来的机械感。辅助灰使用旧纸色（#E5E0D8），强调色使用修正红（#FF4D4D），少量蓝色（#2D5DA1）作为手写标记或聚焦状态。
+# Font
+- 使用「沐瑶软笔手写体」作为标题字体，字重偏粗，像粗毡尖笔写出的标题。（https://resource-static.bj.bcebos.com/fonts-skill/MuyaoSoftbrush_Regular.ttf）
+- 使用「资源圆体」作为正文字体，保持清晰可读，同时保留手写感。（https://resource-static.bj.bcebos.com/fonts-skill/ResourceHanRoundedCN-Regular.ttf）
+# Animation
+- 触摸时元素产生轻微位移，阴影从 `4px 4px 0` 缩短到 `2px 2px 0`，形成纸片被按下的反馈。
+- 卡片或按钮悬停时可轻微旋转 1-2 度，动作快速直接，像手绘贴纸被轻轻拨动。
+# Layout
+- 页面像草稿本上的拼贴排版，允许轻微错位、重叠和不对称，不追求精确网格。
+- 卡片、图片和提示标签可带有小角度旋转，留白宽松，整体保持“随手整理过”的轻松秩序。
+# Elements
+- 所有按钮、卡片和输入框都使用不规则圆角，避免标准圆角，边框呈现手绘抖动感。
+- 边框使用较粗的铅笔黑实线，辅助分割线可使用虚线，阴影采用无模糊硬偏移效果。
+- 背景叠加淡淡纸张点阵纹理，例如 `radial-gradient(#E5E0D8 1px, transparent 1px)`。
+- 可使用胶带、图钉、虚线箭头、便签标签和涂鸦下划线作为装饰，但保持少量点缀。</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>可爱极简</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>粉彩色系，圆润形状，轻盈留白，带有日系卡哇伊气质的极简风格。整体温柔、清爽、亲近，强调可爱但不杂乱。</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="W131" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Theme Name: 可爱极简
+# Vibe &amp; Description:
+粉彩色系，圆润形状，轻盈留白，带有日系卡哇伊气质的极简风格。整体温柔、清爽、亲近，强调可爱但不杂乱。
+# Color
+- 使用低饱和度粉彩色，避免深色背景、荧光色和霓虹发光。
+- 背景使用暖白色（#FFF7ED）或极浅橙白，主色使用柔粉（#F9A8D4），辅助点缀可使用淡紫（#A78BFA）、浅青（#67E8F9）、淡黄（#FDE68A）。文字使用柔和深灰，保持清晰但不生硬。
+# Font
+- 使用「资源圆体」作为标题字体。（https://resource-static.bj.bcebos.com/fonts-skill/ResourceHanRoundedCN-Bold.ttf）
+- 使用「HarmonyOS Sans」作为正文字体。（https://resource-static.bj.bcebos.com/fonts-skill/HarmonyOSSans_Regular.ttf）
+## 字体引入方式
+在 `app/_layout.tsx` 中加载字体
+```js
+import { useFonts } from 'expo-font';
+const [fontsLoaded] = useFonts({
+  'ResourceHanRoundedCN-Bold': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/ResourceHanRoundedCN-Bold.ttf' },
+  'HarmonyOSSans-Regular': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/HarmonyOSSans_Regular.ttf' },
+});
+```
+`tailwind.config.js` 添加 fontFamily 属性扩展字体
+```js
+{
+  fontFamily: {
+    'title-resource-rounded': ['ResourceHanRoundedCN-Bold', 'sans-serif'],
+    'body-harmony': ['HarmonyOSSans-Regular', 'sans-serif'],
+  }
+}
+```
+## 字体使用示例
+```jsx
+&lt;Text className="font-title-resource-rounded text-3xl"&gt;&lt;/Text&gt;
+&lt;Text className="font-body-harmony text-base"&gt;&lt;/Text&gt;
+```
+# Animation
+- 点击时使用轻微回弹反馈，元素先缩小再恢复，像柔软糖果被按压。
+- Hover 或触摸反馈采用 `scale-105`、`active:scale-95`，过渡时长约 200ms，并使用带回弹感的缓动曲线。
+- 元素出现时可使用淡入、轻微上浮或小幅摇摆，避免生硬线性动画。
+# Layout
+- 页面保持宽松留白，信息密度低，整体像柔软的粉彩卡片被轻轻摆放在暖白背景上。
+- 卡片、按钮和输入框统一使用大圆角，常用 `rounded-2xl`、`rounded-3xl`、`rounded-full`。
+- 移动端触控目标不低于 44px，间距舒适，重点内容通过颜色深浅、字号和留白建立层级。
+# Elements
+- 按钮使用粉彩纯色或柔和渐变，圆角胶囊形，带轻微缩放反馈。
+- 卡片使用白色或暖白背景，搭配柔和阴影 `shadow-sm` / `shadow-md`，可添加浅粉边框 `border-2 border-pink-200`。
+- 输入框使用圆润边框和粉彩聚焦外圈，如 `focus:ring-4 focus:ring-pink-100`。
+- 避免黑色粗边框、强阴影、小圆角和任何霓虹发光效果。
+</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>可爱极简</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>粉彩色系，圆润形状，轻盈留白，带有日系卡哇伊气质的极简风格。整体温柔、清爽、亲近，强调可爱但不杂乱。</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Web, MiniProgram</t>
+        </is>
+      </c>
+      <c r="W132" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t># Theme Name: 可爱极简
+# Vibe &amp; Description:
+粉彩色系，圆润形状，轻盈留白，带有日系卡哇伊气质的极简风格。整体温柔、清爽、亲近，强调可爱但不杂乱。
+# Color
+- 使用低饱和度粉彩色，避免深色背景、荧光色和霓虹发光。
+- 背景使用暖白色（#FFF7ED）或极浅橙白，主色使用柔粉（#F9A8D4），辅助点缀可使用淡紫（#A78BFA）、浅青（#67E8F9）、淡黄（#FDE68A）。文字使用柔和深灰，保持清晰但不生硬。
+# Font
+- 使用「资源圆体」作为标题字体。（https://resource-static.bj.bcebos.com/fonts-skill/ResourceHanRoundedCN-Bold.ttf）
+- 使用「HarmonyOS Sans」作为正文字体。（https://resource-static.bj.bcebos.com/fonts-skill/HarmonyOSSans_Regular.ttf）
+# Animation
+- 点击时使用轻微回弹反馈，元素先缩小再恢复，像柔软糖果被按压。
+- Hover 或触摸反馈采用 `scale-105`、`active:scale-95`，过渡时长约 200ms，并使用带回弹感的缓动曲线。
+- 元素出现时可使用淡入、轻微上浮或小幅摇摆，避免生硬线性动画。
+# Layout
+- 页面保持宽松留白，信息密度低，整体像柔软的粉彩卡片被轻轻摆放在暖白背景上。
+- 卡片、按钮和输入框统一使用大圆角，常用 `rounded-2xl`、`rounded-3xl`、`rounded-full`。
+- 移动端触控目标不低于 44px，间距舒适，重点内容通过颜色深浅、字号和留白建立层级。
+# Elements
+- 按钮使用粉彩纯色或柔和渐变，圆角胶囊形，带轻微缩放反馈。
+- 卡片使用白色或暖白背景，搭配柔和阴影 `shadow-sm` / `shadow-md`，可添加浅粉边框 `border-2 border-pink-200`。
+- 输入框使用圆润边框和粉彩聚焦外圈，如 `focus:ring-4 focus:ring-pink-100`。
+- 避免黑色粗边框、强阴影、小圆角和任何霓虹发光效果。</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>国风古韵</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>宋韵东方美学，宣纸纹理与青绿山水暗纹交织，温润雅致、古籍画册感强，强调留白、题跋、印章与书画气韵。</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="W133" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Theme Name: 国风古韵
+# Vibe &amp; Description:
+宋韵东方美学，宣纸纹理与青绿山水暗纹交织，温润雅致、古籍画册感强，强调留白、题跋、印章与书画气韵。
+# Color
+- 使用低饱和、温润的古风色彩，避免纯白、纯黑和高饱和荧光色。
+- 背景使用浅米黄宣纸色（#F9F6EF / #F5EEDC），叠加低透明度古画暗纹。文字使用墨黑（#2C2C2C），主视觉使用石青（#2D5A6E）与石绿（#5B7A5A），边框和分割线使用古棕褐（#8B6B4D），重点强调使用朱砂红（#C43B2B）。
+# Font
+- 使用「思源宋体」作为标题字体，呈现毛笔书法的古韵气质。（https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-SemiBold.woff2）
+- 使用「思源宋体」作为正文字体，保持文楷的温润感与移动端可读性。（https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-Regular.woff2）
+## 字体引入方式
+在 `app/_layout.tsx` 中加载字体
+```js
+import { useFonts } from 'expo-font';
+const [fontsLoaded] = useFonts({
+  'SourceHanSerifCN-SemiBold': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-SemiBold.woff2' },
+  'SourceHanSerifCN-Regular': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-Regular.woff2' },
+});
+```
+`tailwind.config.js` 添加 fontFamily 属性扩展字体
+```js
+{
+  fontFamily: {
+    'title-serif-semibold': ['SourceHanSerifCN-SemiBold', 'serif'],
+    'body-serif': ['SourceHanSerifCN-Regular', 'serif'],
+  }
+}
+```
+## 字体使用示例
+```jsx
+&lt;Text className="font-title-serif-semibold text-3xl"&gt;&lt;/Text&gt;
+&lt;Text className="font-body-serif text-base"&gt;&lt;/Text&gt;
+```
+# Animation
+- 触摸卡片或图标时，元素轻微上浮，边框加深，并以朱砂红作为高亮反馈。
+- 点击印章或重点按钮时，使用短暂的“盖印”动效（scale 0.95→1.05→1），带来朱砂落纸的仪式感。
+- 页面元素出现时可采用“画卷展开”或“淡入+轻微位移”，悬浮状态可加入低透明墨色晕染过渡。
+# Layout
+- 移动端采用古籍画册式纵向排布，卡片堆叠呈现，保留充足留白与对称感。
+- Banner 可使用居中或题跋式偏置布局，标题醒目，周围留出宣纸呼吸感。
+- 内容卡片遵循仿古题跋结构：标题、正文、作者信息与朱砂印章依次呈现，行高宽松，阅读节奏舒缓。
+# Elements
+- 背景使用浅米黄宣纸纹理，并叠加低饱和青绿山水、古画或水墨祥云暗纹。
+- 卡片使用做旧纸张质感，细棕线边框，圆角控制在 0-4px，避免现代感过强。
+- 功能入口使用圆形古风线描图标，可包含山水、楼阁、画卷、毛笔、祥云等元素。
+- 装饰元素以朱砂印章、水墨纹样、卷轴边饰和古风细线为主，保持克制，不使用玻璃拟态、炫光渐变或厚重阴影。
+</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>国风古韵</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>宋韵东方美学，宣纸纹理与青绿山水暗纹交织，温润雅致、古籍画册感强，强调留白、题跋、印章与书画气韵。</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Web, MiniProgram</t>
+        </is>
+      </c>
+      <c r="W134" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t># Theme Name: 国风古韵
+# Vibe &amp; Description:
+宋韵东方美学，宣纸纹理与青绿山水暗纹交织，温润雅致、古籍画册感强，强调留白、题跋、印章与书画气韵。
+# Color
+- 使用低饱和、温润的古风色彩，避免纯白、纯黑和高饱和荧光色。
+- 背景使用浅米黄宣纸色（#F9F6EF / #F5EEDC），叠加低透明度古画暗纹。文字使用墨黑（#2C2C2C），主视觉使用石青（#2D5A6E）与石绿（#5B7A5A），边框和分割线使用古棕褐（#8B6B4D），重点强调使用朱砂红（#C43B2B）。
+# Font
+- 使用「思源宋体」作为标题字体，呈现毛笔书法的古韵气质。（https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-SemiBold.woff2）
+- 使用「思源宋体」作为正文字体，保持文楷的温润感与移动端可读性。（https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-Regular.woff2）
+# Animation
+- 触摸卡片或图标时，元素轻微上浮，边框加深，并以朱砂红作为高亮反馈。
+- 点击印章或重点按钮时，使用短暂的“盖印”动效（scale 0.95→1.05→1），带来朱砂落纸的仪式感。
+- 页面元素出现时可采用“画卷展开”或“淡入+轻微位移”，悬浮状态可加入低透明墨色晕染过渡。
+# Layout
+- 移动端采用古籍画册式纵向排布，卡片堆叠呈现，保留充足留白与对称感。
+- Banner 可使用居中或题跋式偏置布局，标题醒目，周围留出宣纸呼吸感。
+- 内容卡片遵循仿古题跋结构：标题、正文、作者信息与朱砂印章依次呈现，行高宽松，阅读节奏舒缓。
+# Elements
+- 背景使用浅米黄宣纸纹理，并叠加低饱和青绿山水、古画或水墨祥云暗纹。
+- 卡片使用做旧纸张质感，细棕线边框，圆角控制在 0-4px，避免现代感过强。
+- 功能入口使用圆形古风线描图标，可包含山水、楼阁、画卷、毛笔、祥云等元素。
+- 装饰元素以朱砂印章、水墨纹样、卷轴边饰和古风细线为主，保持克制，不使用玻璃拟态、炫光渐变或厚重阴影。</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>非洲布艺</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>西非 Kente 编织与 Adire 扎染启发的视觉风格，大胆几何、大地暖色、粗粝织物质感，呈现手工纺织的文化厚度与鲜明节奏。</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="W135" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Theme Name: 非洲布艺
+# Vibe &amp; Description:
+西非 Kente 编织与 Adire 扎染启发的视觉风格，大胆几何、大地暖色、粗粝织物质感，呈现手工纺织的文化厚度与鲜明节奏。
+# Color
+- 使用深木色、赤陶橙、沙金色、沙色和森林绿，避免纯白、粉彩、霓虹色。
+- 背景以深木色（#2C1810）建立厚重基底，卡片使用沙色（#E8D5B5），强调色使用 Kente 橙（#C4501F）与金色（#F0C75E），森林绿（#1A5632）用于装饰文字或局部点缀，形成大地色与鲜明色块的碰撞。
+# Font
+- 使用「思源宋体」作为标题字体，搭配大写感、粗字重和宽字距。（https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-Bold.woff2）
+- 使用「HarmonyOS Sans」作为正文字体，保持清晰、稳定、带有人文温度的阅读体验。（https://resource-static.bj.bcebos.com/fonts-skill/HarmonyOSSans_Regular.ttf）
+## 字体引入方式
+在 `app/_layout.tsx` 中加载字体
+```js
+import { useFonts } from 'expo-font';
+const [fontsLoaded] = useFonts({
+  'SourceHanSerifCN-Bold': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-Bold.woff2' },
+  'HarmonyOSSans-Regular': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/HarmonyOSSans_Regular.ttf' },
+});
+```
+`tailwind.config.js` 添加 fontFamily 属性扩展字体
+```js
+{
+  fontFamily: {
+    'serif-title': ['SourceHanSerifCN-Bold', 'serif', 'sans-serif'],
+    'harmony-body': ['HarmonyOSSans-Regular', 'sans-serif'],
+  }
+}
+```
+## 字体使用示例
+```jsx
+&lt;Text className="font-serif-title text-3xl"&gt;&lt;/Text&gt;
+&lt;Text className="font-harmony-body text-base"&gt;&lt;/Text&gt;
+```
+# Animation
+- 点击时以硬边阴影变化作为主要反馈，避免柔软漂浮感；按钮和卡片可从 `2px` 阴影切换到 `4px/6px` 阴影。
+- 元素出现时采用短促的淡入与轻微缩放，模拟织物图案展开；交互节奏保持干脆、有重量。
+# Layout
+- 页面采用强几何分区：深色背景承载主视觉，沙色卡片承载内容，粗边框明确切割信息层级。
+- 移动端以单列卡片为主，区块之间留出充足间距；标题大、粗、宽字距，形成类似 Kente 条纹的节奏感。
+# Elements
+- 卡片和按钮使用 `border-2`、`rounded-lg`、硬边偏移阴影，避免全圆角、玻璃拟态和模糊效果。
+- 装饰元素采用几何条纹、色块拼接、编织网格或扎染纹理，控制使用比例，避免喧宾夺主。
+- 背景可叠加粗糙织物噪点；分割线和边框保持厚重、明确，呈现手工布料的不完美边缘。
+</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>非洲布艺</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>西非 Kente 编织与 Adire 扎染启发的视觉风格，大胆几何、大地暖色、粗粝织物质感，呈现手工纺织的文化厚度与鲜明节奏。</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Web, MiniProgram</t>
+        </is>
+      </c>
+      <c r="W136" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t># Theme Name: 非洲布艺
+# Vibe &amp; Description:
+西非 Kente 编织与 Adire 扎染启发的视觉风格，大胆几何、大地暖色、粗粝织物质感，呈现手工纺织的文化厚度与鲜明节奏。
+# Color
+- 使用深木色、赤陶橙、沙金色、沙色和森林绿，避免纯白、粉彩、霓虹色。
+- 背景以深木色（#2C1810）建立厚重基底，卡片使用沙色（#E8D5B5），强调色使用 Kente 橙（#C4501F）与金色（#F0C75E），森林绿（#1A5632）用于装饰文字或局部点缀，形成大地色与鲜明色块的碰撞。
+# Font
+- 使用「思源宋体」作为标题字体，搭配大写感、粗字重和宽字距。（https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-Bold.woff2）
+- 使用「HarmonyOS Sans」作为正文字体，保持清晰、稳定、带有人文温度的阅读体验。（https://resource-static.bj.bcebos.com/fonts-skill/HarmonyOSSans_Regular.ttf）
+# Animation
+- 点击时以硬边阴影变化作为主要反馈，避免柔软漂浮感；按钮和卡片可从 `2px` 阴影切换到 `4px/6px` 阴影。
+- 元素出现时采用短促的淡入与轻微缩放，模拟织物图案展开；交互节奏保持干脆、有重量。
+# Layout
+- 页面采用强几何分区：深色背景承载主视觉，沙色卡片承载内容，粗边框明确切割信息层级。
+- 移动端以单列卡片为主，区块之间留出充足间距；标题大、粗、宽字距，形成类似 Kente 条纹的节奏感。
+# Elements
+- 卡片和按钮使用 `border-2`、`rounded-lg`、硬边偏移阴影，避免全圆角、玻璃拟态和模糊效果。
+- 装饰元素采用几何条纹、色块拼接、编织网格或扎染纹理，控制使用比例，避免喧宾夺主。
+- 背景可叠加粗糙织物噪点；分割线和边框保持厚重、明确，呈现手工布料的不完美边缘。</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>报纸美学</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>新闻纸纹理，高对比黑白，零圆角几何结构，强调清晰网格、编辑权威感与纸媒头版的严肃秩序。</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="W137" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Theme Name: 报纸美学
+# Vibe &amp; Description:
+新闻纸纹理，高对比黑白，零圆角几何结构，强调清晰网格、编辑权威感与纸媒头版的严肃秩序。
+# Color
+- 以新闻纸米白、墨黑和编辑红构成严格色彩体系，避免丰富渐变和装饰性色彩。
+- 背景使用温暖纸张色（#F9F9F7），文字与边框使用墨黑（#111111），辅助分隔使用浅灰（#E5E5E0）。强调色仅使用编辑红（#CC0000），用于突发标签、关键按钮或少量状态提示，保持整体克制、可信、锋利。
+# Font
+- 使用「阿里巴巴普惠体3.0」作为标题字体，营造醒目的报纸头版标题感。（https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_SemiBold.ttf）
+- 使用「阿里巴巴普惠体3.0」作为正文字体，保证移动端阅读清晰。（https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf）
+## 字体引入方式
+在 `app/_layout.tsx` 中加载字体
+```js
+import { useFonts } from 'expo-font';
+const [fontsLoaded] = useFonts({
+  'AlibabaPuHuiTi-SemiBold': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_SemiBold.ttf' },
+  'AlibabaPuHuiTi-Regular': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf' },
+});
+```
+`tailwind.config.js` 添加 fontFamily 属性扩展字体
+```js
+{
+  fontFamily: {
+    'alibaba-puhuiti-title': ['AlibabaPuHuiTi-SemiBold', 'sans-serif'],
+    'alibaba-puhuiti-body': ['AlibabaPuHuiTi-Regular', 'sans-serif'],
+  }
+}
+```
+## 字体使用示例
+```jsx
+&lt;Text className="font-alibaba-puhuiti-title text-3xl"&gt;&lt;/Text&gt;
+&lt;Text className="font-alibaba-puhuiti-body text-base"&gt;&lt;/Text&gt;
+```
+# Animation
+- 交互反馈应快速、硬朗、直接。按钮点击时采用黑白反转，卡片按压时产生轻微位移和硬阴影偏移，模拟报纸剪贴被按下的触感。
+- 禁止柔和弹性动画、模糊、渐变和漂浮阴影。页面切换和元素出现可使用短促的淡入或纵向位移，保持编辑版面的冷静节奏。
+# Layout
+- 移动端采用紧凑的报纸专栏式布局，通过粗细分明的边框、分隔线和模块拼接形成清晰版面。
+- 顶部保留报头、日期、卷号或版本信息；内容区可使用非对称卡片、头条区、滚动新闻条和倒置黑底区，营造头版信息密度。
+- 所有模块共享边界，减少多余留白。标题可占据较大视觉面积，正文保持两端对齐或整齐分栏感。
+# Elements
+- 所有按钮、卡片、输入框和图片容器必须保持 0 圆角，边框使用 1px 墨黑线，重点区域可使用 4px 粗线。
+- 背景叠加轻微点阵或纸张噪点纹理，局部可使用线条网格增强新闻纸触感。
+- 图片默认使用灰度滤镜，触摸或悬停状态可加入轻微复古棕褐色效果。
+- 标签、导航、日期、作者和分类信息使用小字号大写、宽字距和等宽风格。
+- 重点链接使用粗下划线或编辑红点缀，按钮默认黑底白字，触发状态反转为白底黑字。
+</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>报纸美学</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>新闻纸纹理，高对比黑白，零圆角几何结构，强调清晰网格、编辑权威感与纸媒头版的严肃秩序。</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Web, MiniProgram</t>
+        </is>
+      </c>
+      <c r="W138" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t># Theme Name: 报纸美学
+# Vibe &amp; Description:
+新闻纸纹理，高对比黑白，零圆角几何结构，强调清晰网格、编辑权威感与纸媒头版的严肃秩序。
+# Color
+- 以新闻纸米白、墨黑和编辑红构成严格色彩体系，避免丰富渐变和装饰性色彩。
+- 背景使用温暖纸张色（#F9F9F7），文字与边框使用墨黑（#111111），辅助分隔使用浅灰（#E5E5E0）。强调色仅使用编辑红（#CC0000），用于突发标签、关键按钮或少量状态提示，保持整体克制、可信、锋利。
+# Font
+- 使用「阿里巴巴普惠体3.0」作为标题字体，营造醒目的报纸头版标题感。（https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_SemiBold.ttf）
+- 使用「阿里巴巴普惠体3.0」作为正文字体，保证移动端阅读清晰。（https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf）
+# Animation
+- 交互反馈应快速、硬朗、直接。按钮点击时采用黑白反转，卡片按压时产生轻微位移和硬阴影偏移，模拟报纸剪贴被按下的触感。
+- 禁止柔和弹性动画、模糊、渐变和漂浮阴影。页面切换和元素出现可使用短促的淡入或纵向位移，保持编辑版面的冷静节奏。
+# Layout
+- 移动端采用紧凑的报纸专栏式布局，通过粗细分明的边框、分隔线和模块拼接形成清晰版面。
+- 顶部保留报头、日期、卷号或版本信息；内容区可使用非对称卡片、头条区、滚动新闻条和倒置黑底区，营造头版信息密度。
+- 所有模块共享边界，减少多余留白。标题可占据较大视觉面积，正文保持两端对齐或整齐分栏感。
+# Elements
+- 所有按钮、卡片、输入框和图片容器必须保持 0 圆角，边框使用 1px 墨黑线，重点区域可使用 4px 粗线。
+- 背景叠加轻微点阵或纸张噪点纹理，局部可使用线条网格增强新闻纸触感。
+- 图片默认使用灰度滤镜，触摸或悬停状态可加入轻微复古棕褐色效果。
+- 标签、导航、日期、作者和分类信息使用小字号大写、宽字距和等宽风格。
+- 重点链接使用粗下划线或编辑红点缀，按钮默认黑底白字，触发状态反转为白底黑字。</t>
+        </is>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>可爱轻氧</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>日系可爱与极简留白结合，粉彩、圆润、轻盈、温柔。整体像一口柔软的氧气，亲和但不幼稚，可爱但不杂乱。</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="W139" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Theme Name: 可爱轻氧
+# Vibe &amp; Description:
+日系可爱与极简留白结合，粉彩、圆润、轻盈、温柔。整体像一口柔软的氧气，亲和但不幼稚，可爱但不杂乱。
+# Color
+- 使用低饱和粉彩色系，避免深色背景、荧光色和强对比色。
+- 背景以暖白和浅奶油色为主（#FFF7ED / #FFF9F2），主色使用柔粉（#F9A8D4），辅助点缀可使用浅紫（#A78BFA）、浅青（#67E8F9）、浅黄（#FDE68A）。文字使用柔和深灰（#4B5563），弱化纯黑带来的压迫感。
+- 卡片多使用白色或浅粉底色，边框使用粉彩浅色（如 #FBCFE8），营造轻、软、干净的视觉氛围。
+# Font
+- 使用「资源圆体」作为标题字体。（https://resource-static.bj.bcebos.com/fonts-skill/ResourceHanRoundedCN-Bold.ttf）
+- 使用「HarmonyOS Sans」作为正文字体。（https://resource-static.bj.bcebos.com/fonts-skill/HarmonyOSSans_Regular.ttf）
+## 字体引入方式
+在 `app/_layout.tsx` 中加载字体
+```js
+import { useFonts } from 'expo-font';
+const [fontsLoaded] = useFonts({
+  'ResourceHanRoundedCN-Bold': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/ResourceHanRoundedCN-Bold.ttf' },
+  'HarmonyOSSans-Regular': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/HarmonyOSSans_Regular.ttf' },
+});
+```
+`tailwind.config.js` 添加 fontFamily 属性扩展字体
+```js
+{
+  fontFamily: {
+    'title-resource-rounded': ['ResourceHanRoundedCN-Bold', 'sans-serif'],
+    'body-harmony': ['HarmonyOSSans-Regular', 'sans-serif'],
+  }
+}
+```
+## 字体使用示例
+```jsx
+&lt;Text className="font-title-resource-rounded text-3xl"&gt;&lt;/Text&gt;
+&lt;Text className="font-body-harmony text-base"&gt;&lt;/Text&gt;
+```
+# Animation
+- 点击时使用轻微缩放反馈，如 `active:scale-95`，让元素像软糖一样被轻轻按下。
+- 状态变化采用 `transition-all duration-200`，可加入细腻弹跳、摇摆或淡入效果，但避免夸张动效和强烈位移。
+# Layout
+- 页面保持充足留白，内容分区清晰，使用大圆角卡片承载信息。
+- 主要结构适合移动端：顶部简洁导航或标题区，中部使用纵向卡片流，关键操作按钮固定在视觉焦点附近。
+- 卡片内边距舒展，常用 `p-6`，圆角使用 `rounded-2xl`、`rounded-3xl`，按钮使用 `rounded-full`。
+# Elements
+- 按钮使用柔粉底色、白色文字、圆 pill 形态：`bg-pink-400 text-white rounded-full shadow-md`。
+- 卡片使用白色或浅粉背景，搭配 `border-2 border-pink-200` 与柔和阴影，悬停或触摸时只增强阴影，不使用硬偏移阴影。
+- 进度、完成状态、习惯追踪等组件可使用圆点组、圆形进度条或柔和长条，颜色保持粉彩统一。
+- 装饰元素使用半透明圆点、圆圈、圆角漂浮块，避免尖锐直角、黑色背景、霓虹光效和粗重字体。
+</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>可爱轻氧</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>日系可爱与极简留白结合，粉彩、圆润、轻盈、温柔。整体像一口柔软的氧气，亲和但不幼稚，可爱但不杂乱。</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Web, MiniProgram</t>
+        </is>
+      </c>
+      <c r="W140" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t># Theme Name: 可爱轻氧
+# Vibe &amp; Description:
+日系可爱与极简留白结合，粉彩、圆润、轻盈、温柔。整体像一口柔软的氧气，亲和但不幼稚，可爱但不杂乱。
+# Color
+- 使用低饱和粉彩色系，避免深色背景、荧光色和强对比色。
+- 背景以暖白和浅奶油色为主（#FFF7ED / #FFF9F2），主色使用柔粉（#F9A8D4），辅助点缀可使用浅紫（#A78BFA）、浅青（#67E8F9）、浅黄（#FDE68A）。文字使用柔和深灰（#4B5563），弱化纯黑带来的压迫感。
+- 卡片多使用白色或浅粉底色，边框使用粉彩浅色（如 #FBCFE8），营造轻、软、干净的视觉氛围。
+# Font
+- 使用「资源圆体」作为标题字体。（https://resource-static.bj.bcebos.com/fonts-skill/ResourceHanRoundedCN-Bold.ttf）
+- 使用「HarmonyOS Sans」作为正文字体。（https://resource-static.bj.bcebos.com/fonts-skill/HarmonyOSSans_Regular.ttf）
+# Animation
+- 点击时使用轻微缩放反馈，如 `active:scale-95`，让元素像软糖一样被轻轻按下。
+- 状态变化采用 `transition-all duration-200`，可加入细腻弹跳、摇摆或淡入效果，但避免夸张动效和强烈位移。
+# Layout
+- 页面保持充足留白，内容分区清晰，使用大圆角卡片承载信息。
+- 主要结构适合移动端：顶部简洁导航或标题区，中部使用纵向卡片流，关键操作按钮固定在视觉焦点附近。
+- 卡片内边距舒展，常用 `p-6`，圆角使用 `rounded-2xl`、`rounded-3xl`，按钮使用 `rounded-full`。
+# Elements
+- 按钮使用柔粉底色、白色文字、圆 pill 形态：`bg-pink-400 text-white rounded-full shadow-md`。
+- 卡片使用白色或浅粉背景，搭配 `border-2 border-pink-200` 与柔和阴影，悬停或触摸时只增强阴影，不使用硬偏移阴影。
+- 进度、完成状态、习惯追踪等组件可使用圆点组、圆形进度条或柔和长条，颜色保持粉彩统一。
+- 装饰元素使用半透明圆点、圆圈、圆角漂浮块，避免尖锐直角、黑色背景、霓虹光效和粗重字体。</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>极简商务风</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>古典衬线字体，冷灰纸感背景，克制蓝色点缀，以细线、留白和编辑感排版营造安静、精致、可信赖的商务气质。</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="W141" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Theme Name: 极简商务风
+# Vibe &amp; Description:
+古典衬线字体，冷灰纸感背景，克制蓝色点缀，以细线、留白和编辑感排版营造安静、精致、可信赖的商务气质。
+# Color
+- 色彩保持极度克制，以冷灰、深黑、纯白和蓝色作为唯一强调色。
+- 背景使用冷灰纸感色（#F9F9F9），主要文字使用深邃黑（#1A1A1A），卡片表面使用纯白（#FFFFFF），强调色使用清透蓝（#1C82F5）。整体避免高饱和与强对比，呈现出版物般的耐读与优雅。
+# Font
+- 使用「思源宋体」作为标题字体。（https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-SemiBold.woff2）
+- 使用「阿里巴巴普惠体3.0」作为正文字体。（https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf）
+## 字体引入方式
+在 `app/_layout.tsx` 中加载字体
+```js
+import { useFonts } from 'expo-font';
+const [fontsLoaded] = useFonts({
+  'SourceHanSerifCN-SemiBold': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-SemiBold.woff2' },
+  'AlibabaPuHuiTi-Regular': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf' },
+});
+```
+`tailwind.config.js` 添加 fontFamily 属性扩展字体
+```js
+{
+  fontFamily: {
+    'title-serif-semibold': ['SourceHanSerifCN-SemiBold', 'serif'],
+    'body-alibaba': ['AlibabaPuHuiTi-Regular', 'sans-serif', 'serif'],
+  }
+}
+```
+## 字体使用示例
+```jsx
+&lt;Text className="font-title-serif-semibold text-3xl"&gt;&lt;/Text&gt;
+&lt;Text className="font-body-alibaba text-base"&gt;&lt;/Text&gt;
+```
+# Animation
+- 动效克制、平滑、无弹跳。按钮触摸时轻微上浮或回落，卡片仅通过阴影、边框和背景明度变化表达状态。
+- 元素出现采用缓慢淡入，时长约 200-600ms，强调安静、稳定、编辑级的阅读节奏。
+# Layout
+- 页面采用宽松留白与窄内容列，形成高级出版物的阅读感。移动端保持充分边距，避免信息拥挤。
+- 章节之间用 1px 冷灰细线建立秩序，标题居中或轻微不对称排列，卡片间距舒展，正文行高保持宽松。
+# Elements
+- 按钮使用 6px 圆角，主按钮为蓝色背景白字，辅助按钮为细边框轮廓，交互时只做轻微明度与阴影变化。
+- 卡片使用白色背景、8px 圆角、细灰边框和极淡阴影，可在顶部加入 2px 蓝色强调线。
+- 章节标签采用等宽小型大写、宽字距，并配合左右贯穿细线，形成标志性的编辑感结构。
+- 背景可叠加极淡纸张噪点和低透明度蓝色光晕，但必须保持干净、冷静和克制。
+</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>极简商务风</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>古典衬线字体，冷灰纸感背景，克制蓝色点缀，以细线、留白和编辑感排版营造安静、精致、可信赖的商务气质。</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Web, MiniProgram</t>
+        </is>
+      </c>
+      <c r="W142" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t># Theme Name: 极简商务风
+# Vibe &amp; Description:
+古典衬线字体，冷灰纸感背景，克制蓝色点缀，以细线、留白和编辑感排版营造安静、精致、可信赖的商务气质。
+# Color
+- 色彩保持极度克制，以冷灰、深黑、纯白和蓝色作为唯一强调色。
+- 背景使用冷灰纸感色（#F9F9F9），主要文字使用深邃黑（#1A1A1A），卡片表面使用纯白（#FFFFFF），强调色使用清透蓝（#1C82F5）。整体避免高饱和与强对比，呈现出版物般的耐读与优雅。
+# Font
+- 使用「思源宋体」作为标题字体。（https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-SemiBold.woff2）
+- 使用「阿里巴巴普惠体3.0」作为正文字体。（https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf）
+# Animation
+- 动效克制、平滑、无弹跳。按钮触摸时轻微上浮或回落，卡片仅通过阴影、边框和背景明度变化表达状态。
+- 元素出现采用缓慢淡入，时长约 200-600ms，强调安静、稳定、编辑级的阅读节奏。
+# Layout
+- 页面采用宽松留白与窄内容列，形成高级出版物的阅读感。移动端保持充分边距，避免信息拥挤。
+- 章节之间用 1px 冷灰细线建立秩序，标题居中或轻微不对称排列，卡片间距舒展，正文行高保持宽松。
+# Elements
+- 按钮使用 6px 圆角，主按钮为蓝色背景白字，辅助按钮为细边框轮廓，交互时只做轻微明度与阴影变化。
+- 卡片使用白色背景、8px 圆角、细灰边框和极淡阴影，可在顶部加入 2px 蓝色强调线。
+- 章节标签采用等宽小型大写、宽字距，并配合左右贯穿细线，形成标志性的编辑感结构。
+- 背景可叠加极淡纸张噪点和低透明度蓝色光晕，但必须保持干净、冷静和克制。</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>漫画书风格</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>粗黑描边，高饱和印刷色，不规则分格与夸张动势，营造热血、冒险、英雄叙事感。</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="W143" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Theme Name: 漫画书风格
+# Vibe &amp; Description:
+粗黑描边，高饱和印刷色，不规则分格与夸张动势，营造热血、冒险、英雄叙事感。
+# Color
+- 使用经典 CMYK 漫画印刷色，色彩明快且对比强烈。
+- 背景使用纸张白（#FFFEF0）或深灰（#2C2C2C），文字与描边使用纯黑（#000000）。主色采用漫画红（#E23636）、英雄蓝（#1E90FF）和警示黄（#FFD700），强调爆发力、速度感和戏剧冲突。
+# Font
+- 使用「庞门正道标题体」作为标题字体。（https://resource-static.bj.bcebos.com/fonts-skill/PangMenTitle_Regular.ttf）
+- 使用「阿里巴巴普惠体3.0」作为正文字体。（https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf）
+## 字体引入方式
+在 `app/_layout.tsx` 中加载字体
+```js
+import { useFonts } from 'expo-font';
+const [fontsLoaded] = useFonts({
+  'PangMenTitle-Regular': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/PangMenTitle_Regular.ttf' },
+  'AlibabaPuHuiTi-Regular': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf' },
+});
+```
+`tailwind.config.js` 添加 fontFamily 属性扩展字体
+```js
+{
+  fontFamily: {
+    'title-pangmen': ['PangMenTitle-Regular', 'sans-serif'],
+    'body-alibaba': ['AlibabaPuHuiTi-Regular', 'sans-serif'],
+  }
+}
+```
+## 字体使用示例
+```jsx
+&lt;Text className="font-title-pangmen text-3xl"&gt;&lt;/Text&gt;
+&lt;Text className="font-body-alibaba text-base"&gt;&lt;/Text&gt;
+```
+# Animation
+- 触摸时元素会轻微缩放或倾斜，模拟漫画分格被推近的镜头感。点击时可出现短暂的爆炸星形或“POW!”音效文字反馈。
+- 元素进入页面时采用快速飞入、弹跳或放射线扩散动画，营造动作场面突然展开的感觉。
+# Layout
+- 页面使用不规则分格布局，卡片可略微倾斜、重叠或破框，形成强烈的叙事节奏。
+- 重要内容使用大分格或跨区域展示，辅助内容保持紧凑，利用对角线构图和夸张透视增强动感。
+# Elements
+- 卡片和按钮使用 2-4px 粗黑实线描边，边角可略带硬朗的漫画切面。
+- 动作线: 在按钮、封面或重点信息周围加入放射状速度线，强化运动感。
+- 对话气泡: 提示、标签和说明可使用椭圆形或云朵状气泡，并保留小尾巴。
+- 半色调点阵: 阴影、背景和过渡区域叠加圆点纹理，模拟复古印刷质感。
+</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>漫画书风格</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>粗黑描边，高饱和印刷色，不规则分格与夸张动势，营造热血、冒险、英雄叙事感。</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Web, MiniProgram</t>
+        </is>
+      </c>
+      <c r="W144" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t># Theme Name: 漫画书风格
+# Vibe &amp; Description:
+粗黑描边，高饱和印刷色，不规则分格与夸张动势，营造热血、冒险、英雄叙事感。
+# Color
+- 使用经典 CMYK 漫画印刷色，色彩明快且对比强烈。
+- 背景使用纸张白（#FFFEF0）或深灰（#2C2C2C），文字与描边使用纯黑（#000000）。主色采用漫画红（#E23636）、英雄蓝（#1E90FF）和警示黄（#FFD700），强调爆发力、速度感和戏剧冲突。
+# Font
+- 使用「庞门正道标题体」作为标题字体。（https://resource-static.bj.bcebos.com/fonts-skill/PangMenTitle_Regular.ttf）
+- 使用「阿里巴巴普惠体3.0」作为正文字体。（https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf）
+# Animation
+- 触摸时元素会轻微缩放或倾斜，模拟漫画分格被推近的镜头感。点击时可出现短暂的爆炸星形或“POW!”音效文字反馈。
+- 元素进入页面时采用快速飞入、弹跳或放射线扩散动画，营造动作场面突然展开的感觉。
+# Layout
+- 页面使用不规则分格布局，卡片可略微倾斜、重叠或破框，形成强烈的叙事节奏。
+- 重要内容使用大分格或跨区域展示，辅助内容保持紧凑，利用对角线构图和夸张透视增强动感。
+# Elements
+- 卡片和按钮使用 2-4px 粗黑实线描边，边角可略带硬朗的漫画切面。
+- 动作线: 在按钮、封面或重点信息周围加入放射状速度线，强化运动感。
+- 对话气泡: 提示、标签和说明可使用椭圆形或云朵状气泡，并保留小尾巴。
+- 半色调点阵: 阴影、背景和过渡区域叠加圆点纹理，模拟复古印刷质感。</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>复古90年代</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>早期互联网与 Windows 95 气质，系统字体，高饱和彩色元素，3D 斜角按钮，跑马灯与建设中能量，营造粗糙、热闹、反极简的怀旧网页感。</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="W145" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Theme Name: 复古90年代
+# Vibe &amp; Description:
+早期互联网与 Windows 95 气质，系统字体，高饱和彩色元素，3D 斜角按钮，跑马灯与建设中能量，营造粗糙、热闹、反极简的怀旧网页感。
+# Color
+- 使用高对比、高饱和的早期系统色，避免柔和色、半透明和现代渐变。
+- 背景使用 Win95 灰（#C0C0C0），文字使用纯黑（#000000），链接使用纯蓝（#0000FF），已访问为紫色（#800080），悬停为红色（#FF0000）。强调色可使用亮黄（#FFFF00）、亮绿（#00FF00）、亮红（#FF0000），标题栏使用海军蓝到亮蓝（#000080 → #1084D0）。
+# Font
+- 标题「站酷酷黑体」（https://resource-static.bj.bcebos.com/fonts-skill/ZCOOLKuHei_Regular.ttf）
+- 正文，「思源宋体」（https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-Regular.woff2）
+## 字体引入方式
+在 `app/_layout.tsx` 中加载字体
+```js
+import { useFonts } from 'expo-font';
+const [fontsLoaded] = useFonts({
+  'ZCOOLKuHei-Regular': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/ZCOOLKuHei_Regular.ttf' },
+  'SourceHanSerifCN-Regular': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-Regular.woff2' },
+});
+```
+`tailwind.config.js` 添加 fontFamily 属性扩展字体
+```js
+{
+  fontFamily: {
+    'zkkh-title': ['ZCOOLKuHei-Regular', 'sans-serif'],
+    'serif-body': ['SourceHanSerifCN-Regular', 'serif'],
+  }
+}
+```
+## 字体使用示例
+```jsx
+&lt;Text className="font-zkkh-title text-3xl"&gt;&lt;/Text&gt;
+&lt;Text className="font-serif-body text-base"&gt;&lt;/Text&gt;
+```
+# Animation
+- 动效快速、直接、数字化，不使用自然缓动。按钮点击时斜角反转并轻微位移，像真实按下系统控件。
+- 可使用跑马灯文字、彩虹色循环、闪烁“新品！”徽章和命中计数器数字跳动；在 reduced motion 下停止循环动画。
+# Layout
+- 移动端采用单列堆叠，但保留表格式边框、密集信息和横向滚动区域。
+- 页面模拟 90 年代网页窗口：灰色纹理背景、蓝色标题栏、内嵌内容区、可见网格线和凹槽分割线。布局不追求极简留白，而是饱满、热闹、像被精心拼贴的旧网页。
+# Elements
+- 所有按钮、卡片、输入框必须使用 0 圆角和 2px 斜角边框，区分外凸与内嵌状态。
+- 卡片采用窗口样式：蓝色渐变标题栏、白色粗体标题、灰色外框和浅黄或白色内容区。
+- 重点区域使用黄黑施工条纹，搭配闪烁徽章、动态 CTA 或彩色方块装饰。
+- 链接始终带下划线，保持蓝、紫、红三态，不做现代化弱化。
+- 背景可叠加 45 度瓷砖纹理，分割线使用上灰下白的 3D 蚀刻效果。
+</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>复古90年代</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>早期互联网与 Windows 95 气质，系统字体，高饱和彩色元素，3D 斜角按钮，跑马灯与建设中能量，营造粗糙、热闹、反极简的怀旧网页感。</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Web, MiniProgram</t>
+        </is>
+      </c>
+      <c r="W146" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t># Theme Name: 复古90年代
+# Vibe &amp; Description:
+早期互联网与 Windows 95 气质，系统字体，高饱和彩色元素，3D 斜角按钮，跑马灯与建设中能量，营造粗糙、热闹、反极简的怀旧网页感。
+# Color
+- 使用高对比、高饱和的早期系统色，避免柔和色、半透明和现代渐变。
+- 背景使用 Win95 灰（#C0C0C0），文字使用纯黑（#000000），链接使用纯蓝（#0000FF），已访问为紫色（#800080），悬停为红色（#FF0000）。强调色可使用亮黄（#FFFF00）、亮绿（#00FF00）、亮红（#FF0000），标题栏使用海军蓝到亮蓝（#000080 → #1084D0）。
+# Font
+- 标题「站酷酷黑体」（https://resource-static.bj.bcebos.com/fonts-skill/ZCOOLKuHei_Regular.ttf）
+- 正文，「思源宋体」（https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-Regular.woff2）
+# Animation
+- 动效快速、直接、数字化，不使用自然缓动。按钮点击时斜角反转并轻微位移，像真实按下系统控件。
+- 可使用跑马灯文字、彩虹色循环、闪烁“新品！”徽章和命中计数器数字跳动；在 reduced motion 下停止循环动画。
+# Layout
+- 移动端采用单列堆叠，但保留表格式边框、密集信息和横向滚动区域。
+- 页面模拟 90 年代网页窗口：灰色纹理背景、蓝色标题栏、内嵌内容区、可见网格线和凹槽分割线。布局不追求极简留白，而是饱满、热闹、像被精心拼贴的旧网页。
+# Elements
+- 所有按钮、卡片、输入框必须使用 0 圆角和 2px 斜角边框，区分外凸与内嵌状态。
+- 卡片采用窗口样式：蓝色渐变标题栏、白色粗体标题、灰色外框和浅黄或白色内容区。
+- 重点区域使用黄黑施工条纹，搭配闪烁徽章、动态 CTA 或彩色方块装饰。
+- 链接始终带下划线，保持蓝、紫、红三态，不做现代化弱化。
+- 背景可叠加 45 度瓷砖纹理，分割线使用上灰下白的 3D 蚀刻效果。</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>高端服饰</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>静奢留白，高定剪裁，低饱和影像与极细银线共同营造克制、沉浸、具有面料质感的高级服饰浏览体验。</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="W147" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Theme Name: 高端服饰
+# Vibe &amp; Description:
+静奢留白，高定剪裁，低饱和影像与极细银线共同营造克制、沉浸、具有面料质感的高级服饰浏览体验。
+# Color
+- 严格限制色彩，仅使用极夜黑、珍珠白、哑光银、燕麦色和炭灰。
+- 背景使用珍珠白（#FDFBF7）或燕麦色（#F0EDE6），文字使用极夜黑（#111111）与炭灰（#2E2E2E），装饰线使用哑光银（#B0B2B8）。避免高饱和色、渐变和厚重阴影，让服饰材质与留白成为视觉中心。
+# Font
+- 使用「思源宋体」作为标题字体。（https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-Bold.woff2）
+- 使用「阿里巴巴普惠体3.0」作为正文、导航和辅助文字字体。（https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf）
+## 字体引入方式
+在 `app/_layout.tsx` 中加载字体
+```js
+import { useFonts } from 'expo-font';
+const [fontsLoaded] = useFonts({
+  'SourceHanSerifCN-Bold': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-Bold.woff2' },
+  'AlibabaPuHuiTi-Regular': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf' },
+});
+```
+`tailwind.config.js` 添加 fontFamily 属性扩展字体
+```js
+{
+  fontFamily: {
+    'title-serif-bold': ['SourceHanSerifCN-Bold', 'serif'],
+    'body-alibaba': ['AlibabaPuHuiTi-Regular', 'sans-serif'],
+  }
+}
+```
+## 字体使用示例
+```jsx
+&lt;Text className="font-title-serif-bold text-3xl"&gt;&lt;/Text&gt;
+&lt;Text className="font-body-alibaba text-base"&gt;&lt;/Text&gt;
+```
+# Animation
+- 元素出现时采用“淡入 + 上移 24px”的克制动效，时长约 0.5s，营造杂志翻页般的章节感。
+- 触摸商品图时仅做轻微放大、极细银线浮现或“探索 / 预览”文字出现，反馈清晰但不喧宾夺主。
+# Layout
+- 页面以大面积留白塑造奢侈感，内外边距优先使用 32px、64px、96px 等 8 的倍数。
+- 商品内容采用章节式浏览，每个核心区块接近一屏高度，单件服饰居中展示，强调剪裁轮廓与面料纹理。
+- 标题与装饰线保持对齐，形成安静、精准、带有建筑感的视觉秩序。
+# Elements
+- 图片使用低饱和、高对比风格，背景保持纯白或浅灰，突出羊毛、真丝、皮革等材质细节。
+- 按钮使用透明线框样式，边框为极夜黑，触摸时以下划线展开或哑光银变色作为反馈。
+- 分割线、装饰线和悬停边界统一使用 1px 哑光银，避免粗边框、复杂花纹和厚重阴影。
+- 商品卡片不使用默认阴影，依靠留白、银线和轻微缩放建立层次。
+</t>
+        </is>
+      </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>高端服饰</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>静奢留白，高定剪裁，低饱和影像与极细银线共同营造克制、沉浸、具有面料质感的高级服饰浏览体验。</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Web, MiniProgram</t>
+        </is>
+      </c>
+      <c r="W148" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t># Theme Name: 高端服饰
+# Vibe &amp; Description:
+静奢留白，高定剪裁，低饱和影像与极细银线共同营造克制、沉浸、具有面料质感的高级服饰浏览体验。
+# Color
+- 严格限制色彩，仅使用极夜黑、珍珠白、哑光银、燕麦色和炭灰。
+- 背景使用珍珠白（#FDFBF7）或燕麦色（#F0EDE6），文字使用极夜黑（#111111）与炭灰（#2E2E2E），装饰线使用哑光银（#B0B2B8）。避免高饱和色、渐变和厚重阴影，让服饰材质与留白成为视觉中心。
+# Font
+- 使用「思源宋体」作为标题字体。（https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-Bold.woff2）
+- 使用「阿里巴巴普惠体3.0」作为正文、导航和辅助文字字体。（https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf）
+# Animation
+- 元素出现时采用“淡入 + 上移 24px”的克制动效，时长约 0.5s，营造杂志翻页般的章节感。
+- 触摸商品图时仅做轻微放大、极细银线浮现或“探索 / 预览”文字出现，反馈清晰但不喧宾夺主。
+# Layout
+- 页面以大面积留白塑造奢侈感，内外边距优先使用 32px、64px、96px 等 8 的倍数。
+- 商品内容采用章节式浏览，每个核心区块接近一屏高度，单件服饰居中展示，强调剪裁轮廓与面料纹理。
+- 标题与装饰线保持对齐，形成安静、精准、带有建筑感的视觉秩序。
+# Elements
+- 图片使用低饱和、高对比风格，背景保持纯白或浅灰，突出羊毛、真丝、皮革等材质细节。
+- 按钮使用透明线框样式，边框为极夜黑，触摸时以下划线展开或哑光银变色作为反馈。
+- 分割线、装饰线和悬停边界统一使用 1px 哑光银，避免粗边框、复杂花纹和厚重阴影。
+- 商品卡片不使用默认阴影，依靠留白、银线和轻微缩放建立层次。</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>织物质感</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>亚麻、帆布与牛仔般的织物纹理，温和中性色，缝线细节与柔软阴影，营造可触摸、手作感的温暖界面。</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="W149" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Theme Name: 织物质感
+# Vibe &amp; Description:
+亚麻、帆布与牛仔般的织物纹理，温和中性色，缝线细节与柔软阴影，营造可触摸、手作感的温暖界面。
+# Color
+- 使用亚麻色、米白、暖灰作为主背景，避免纯白、纯黑和冷灰。
+- 背景使用浅织物色（#F5F0E8、#FAF7F2、#EDE8E0），文字使用深褐（#3D2E1E）或炭灰（#2C2C2C），辅助文字使用暖灰（#8A7E72）。
+- 点缀色控制在少量范围内，可使用陶土红（#C47D5A）、靛蓝（#4A6A7F）或芥末黄（#D4A84B）。边框与缝线使用暖棕（#C4B5A5），阴影保持低透明度暖灰。
+# Font
+- 使用「沐瑶软笔手写体」作为标题字体，营造温暖、手作、人文感。（https://resource-static.bj.bcebos.com/fonts-skill/MuyaoSoftbrush_Regular.ttf）
+- 使用「思源宋体」作为正文字体，保证织物纹理背景上的清晰可读性。（https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-Regular.woff2）
+## 字体引入方式
+在 `app/_layout.tsx` 中加载字体
+```js
+import { useFonts } from 'expo-font';
+const [fontsLoaded] = useFonts({
+  'MuyaoSoftbrush-Regular': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/MuyaoSoftbrush_Regular.ttf' },
+  'SourceHanSerifCN-Regular': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-Regular.woff2' },
+});
+```
+`tailwind.config.js` 添加 fontFamily 属性扩展字体
+```js
+{
+  fontFamily: {
+    'title-muyao': ['MuyaoSoftbrush-Regular', 'sans-serif'],
+    'body-serif': ['SourceHanSerifCN-Regular', 'serif'],
+  }
+}
+```
+## 字体使用示例
+```jsx
+&lt;Text className="font-title-muyao text-3xl"&gt;&lt;/Text&gt;
+&lt;Text className="font-body-serif text-base"&gt;&lt;/Text&gt;
+```
+# Animation
+- 触摸时元素轻微上浮，阴影加深并伴随低透明高光，像布面被光线掠过。点击时轻微下沉，模拟柔软织物被按压。
+- 动效保持平缓克制，时长约 180-260ms，避免大幅缩放或弹跳效果。
+# Layout
+- 页面采用宽松留白与柔和分区，移动端以单列为主，保持触控目标不低于 44px。
+- 背景始终带有细腻织物纹理，可通过纹理密度、阴影深浅和留白建立层级，避免平整无质感的纯色表面。
+# Elements
+- 按钮与卡片使用亚麻或米白底色，叠加细微织物噪点，并使用暖棕色实线或虚线缝线边框。
+- CTA 可设计成布标风格，使用 6-8px 柔和圆角、双缝线或短线头装饰。
+- 输入框使用浅织物底色和清晰缝线边框，聚焦时边框略加深并增加柔和阴影。
+- 全局纹理可使用 repeating-linear-gradient 模拟经纬线，再叠加极低透明度噪点，形成亚麻、帆布或牛仔的触感。
+</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>织物质感</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>亚麻、帆布与牛仔般的织物纹理，温和中性色，缝线细节与柔软阴影，营造可触摸、手作感的温暖界面。</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Web, MiniProgram</t>
+        </is>
+      </c>
+      <c r="W150" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t># Theme Name: 织物质感
+# Vibe &amp; Description:
+亚麻、帆布与牛仔般的织物纹理，温和中性色，缝线细节与柔软阴影，营造可触摸、手作感的温暖界面。
+# Color
+- 使用亚麻色、米白、暖灰作为主背景，避免纯白、纯黑和冷灰。
+- 背景使用浅织物色（#F5F0E8、#FAF7F2、#EDE8E0），文字使用深褐（#3D2E1E）或炭灰（#2C2C2C），辅助文字使用暖灰（#8A7E72）。
+- 点缀色控制在少量范围内，可使用陶土红（#C47D5A）、靛蓝（#4A6A7F）或芥末黄（#D4A84B）。边框与缝线使用暖棕（#C4B5A5），阴影保持低透明度暖灰。
+# Font
+- 使用「沐瑶软笔手写体」作为标题字体，营造温暖、手作、人文感。（https://resource-static.bj.bcebos.com/fonts-skill/MuyaoSoftbrush_Regular.ttf）
+- 使用「思源宋体」作为正文字体，保证织物纹理背景上的清晰可读性。（https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-Regular.woff2）
+# Animation
+- 触摸时元素轻微上浮，阴影加深并伴随低透明高光，像布面被光线掠过。点击时轻微下沉，模拟柔软织物被按压。
+- 动效保持平缓克制，时长约 180-260ms，避免大幅缩放或弹跳效果。
+# Layout
+- 页面采用宽松留白与柔和分区，移动端以单列为主，保持触控目标不低于 44px。
+- 背景始终带有细腻织物纹理，可通过纹理密度、阴影深浅和留白建立层级，避免平整无质感的纯色表面。
+# Elements
+- 按钮与卡片使用亚麻或米白底色，叠加细微织物噪点，并使用暖棕色实线或虚线缝线边框。
+- CTA 可设计成布标风格，使用 6-8px 柔和圆角、双缝线或短线头装饰。
+- 输入框使用浅织物底色和清晰缝线边框，聚焦时边框略加深并增加柔和阴影。
+- 全局纹理可使用 repeating-linear-gradient 模拟经纬线，再叠加极低透明度噪点，形成亚麻、帆布或牛仔的触感。</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>新粗野主义</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>硬边结构，饱和糖果色块，粗黑描边与明确偏移阴影，整体张扬、俏皮但保持清晰秩序，像彩色积木拼出的界面。</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="W151" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Theme Name: 新粗野主义
+# Vibe &amp; Description:
+硬边结构，饱和糖果色块，粗黑描边与明确偏移阴影，整体张扬、俏皮但保持清晰秩序，像彩色积木拼出的界面。
+# Color
+- 使用高饱和纯色作为主要视觉语言，避免柔和粉彩、低饱和色和大面积渐变。
+- 背景以白色或浅色为主（#FFFFFF），核心色块使用粉色（#FF6B9D）、黄色（#FFD93D）、蓝色（#6BCBFF）、绿色（#6BCB77）。文字、边框与阴影统一使用黑色或深灰（#1A1A1A / #2D2D2D），形成强烈、直接、清晰的视觉对比。
+# Font
+- 使用「优设标题黑」作为标题字体，强调厚重、硬朗和海报感。（https://resource-static.bj.bcebos.com/fonts-skill/YouSheBiaoTiHei_Regular.ttf）
+- 使用「阿里巴巴普惠体3.0」作为正文字体，保持粗黑、清晰、直接的阅读体验。（https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf）
+## 字体引入方式
+在 `app/_layout.tsx` 中加载字体
+```js
+import { useFonts } from 'expo-font';
+const [fontsLoaded] = useFonts({
+  'YouSheBiaoTiHei-Regular': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/YouSheBiaoTiHei_Regular.ttf' },
+  'AlibabaPuHuiTi-Regular': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf' },
+});
+```
+`tailwind.config.js` 添加 fontFamily 属性扩展字体
+```js
+{
+  fontFamily: {
+    'youshe-title': ['YouSheBiaoTiHei-Regular', 'sans-serif'],
+    'alibaba-puhuiti-body': ['AlibabaPuHuiTi-Regular', 'sans-serif'],
+  }
+}
+```
+## 字体使用示例
+```jsx
+&lt;Text className="font-youshe-title text-3xl"&gt;&lt;/Text&gt;
+&lt;Text className="font-alibaba-puhuiti-body text-base"&gt;&lt;/Text&gt;
+```
+# Animation
+- 触摸时元素产生轻微上浮或旋转（-2deg 到 2deg），阴影偏移加重，形成直接、有力的反馈。
+- 点击时元素下沉 2-4px，阴影快速收敛，过渡控制在 120-200ms，避免柔和、拖沓或弹性过强的动画。
+# Layout
+- 页面采用明确的硬边网格与色块分区，信息区域像积木一样清晰拼接。
+- 卡片、按钮和重点模块使用 2-4px 黑色实线边框，搭配 4px 以上的实心偏移阴影，保持强烈层级和秩序感。
+# Elements
+- 按钮和卡片使用饱和色块、粗黑边框和无模糊偏移阴影，形成标志性的新粗野主义组件。
+- 可加入贴纸、手绘箭头、星号、圆圈等涂鸦元素，增加俏皮感，但不能破坏版面清晰度。
+- 背景可少量叠加噪点或条纹纹理，增强质感，但禁止毛玻璃、模糊阴影和复杂渐变。
+- 所有交互元素保持实心、硬边、可点击感强，移动端触摸区域不低于 44px。
+</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>新粗野主义</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>硬边结构，饱和糖果色块，粗黑描边与明确偏移阴影，整体张扬、俏皮但保持清晰秩序，像彩色积木拼出的界面。</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Web, MiniProgram</t>
+        </is>
+      </c>
+      <c r="W152" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t># Theme Name: 新粗野主义
+# Vibe &amp; Description:
+硬边结构，饱和糖果色块，粗黑描边与明确偏移阴影，整体张扬、俏皮但保持清晰秩序，像彩色积木拼出的界面。
+# Color
+- 使用高饱和纯色作为主要视觉语言，避免柔和粉彩、低饱和色和大面积渐变。
+- 背景以白色或浅色为主（#FFFFFF），核心色块使用粉色（#FF6B9D）、黄色（#FFD93D）、蓝色（#6BCBFF）、绿色（#6BCB77）。文字、边框与阴影统一使用黑色或深灰（#1A1A1A / #2D2D2D），形成强烈、直接、清晰的视觉对比。
+# Font
+- 使用「优设标题黑」作为标题字体，强调厚重、硬朗和海报感。（https://resource-static.bj.bcebos.com/fonts-skill/YouSheBiaoTiHei_Regular.ttf）
+- 使用「阿里巴巴普惠体3.0」作为正文字体，保持粗黑、清晰、直接的阅读体验。（https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf）
+# Animation
+- 触摸时元素产生轻微上浮或旋转（-2deg 到 2deg），阴影偏移加重，形成直接、有力的反馈。
+- 点击时元素下沉 2-4px，阴影快速收敛，过渡控制在 120-200ms，避免柔和、拖沓或弹性过强的动画。
+# Layout
+- 页面采用明确的硬边网格与色块分区，信息区域像积木一样清晰拼接。
+- 卡片、按钮和重点模块使用 2-4px 黑色实线边框，搭配 4px 以上的实心偏移阴影，保持强烈层级和秩序感。
+# Elements
+- 按钮和卡片使用饱和色块、粗黑边框和无模糊偏移阴影，形成标志性的新粗野主义组件。
+- 可加入贴纸、手绘箭头、星号、圆圈等涂鸦元素，增加俏皮感，但不能破坏版面清晰度。
+- 背景可少量叠加噪点或条纹纹理，增强质感，但禁止毛玻璃、模糊阴影和复杂渐变。
+- 所有交互元素保持实心、硬边、可点击感强，移动端触摸区域不低于 44px。</t>
+        </is>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>新艺术运动风</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>有机曲线，藤蔓花卉，Mucha 海报感装饰，采用深绿、金色与象牙白调色板，强调优雅、自然与艺术化的流动美感。</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="W153" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Theme Name: 新艺术运动风
+# Vibe &amp; Description:
+有机曲线，藤蔓花卉，Mucha 海报感装饰，采用深绿、金色与象牙白调色板，强调优雅、自然与艺术化的流动美感。
+# Color
+- 使用深绿、金色、象牙白和温暖棕色，避免纯黑、霓虹色和高饱和荧光色。
+- 背景使用象牙白（#F5F0E1）或浅象牙层次（#FAF7EF），文字使用深绿（#2D5016）或深棕色，强调与边框使用金色（#C9A227）。整体配色应像复古展览海报，柔和、精致、带有自然装饰感。
+# Font
+- 使用「思源宋体」作为标题字体。（https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-Bold.woff2）
+- 使用「阿里巴巴普惠体3.0」作为正文字体。（https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf）
+## 字体引入方式
+在 `app/_layout.tsx` 中加载字体
+```js
+import { useFonts } from 'expo-font';
+const [fontsLoaded] = useFonts({
+  'SourceHanSerifCN-Bold': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-Bold.woff2' },
+  'AlibabaPuHuiTi-Regular': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf' },
+});
+```
+`tailwind.config.js` 添加 fontFamily 属性扩展字体
+```js
+{
+  fontFamily: {
+    'title-serif-bold': ['SourceHanSerifCN-Bold', 'serif'],
+    'body-alibaba': ['AlibabaPuHuiTi-Regular', 'sans-serif'],
+  }
+}
+```
+## 字体使用示例
+```jsx
+&lt;Text className="font-title-serif-bold text-3xl"&gt;&lt;/Text&gt;
+&lt;Text className="font-body-alibaba text-base"&gt;&lt;/Text&gt;
+```
+# Animation
+- 触摸时元素轻微上浮，并出现柔和的金色光晕，像光线掠过金箔边框。
+- 元素出现时采用缓慢淡入与细微位移，花卉、藤蔓装饰可做低速漂浮或舒展动画，整体节奏保持柔和、优雅。
+# Layout
+- 页面采用非对称构图，标题与装饰图形形成 60/40 的视觉关系，营造复古海报式层次。
+- 卡片与区块保持宽松留白，使用圆角、金色细边框和柔和阴影，移动端以单列为主，局部可加入花卉分隔线增强节奏。
+# Elements
+- 按钮和卡片使用 `rounded-2xl` 或 `rounded-full`，搭配 `border-2 border-[#C9A227]/60` 与柔和阴影。
+- 藤蔓纹样: 用 SVG 或背景图案作为标题、分割线和卡片角落装饰。
+- 花卉边框: 重要区域可加入圆形花卉框或 Mucha 风格拱形装饰。
+- 强调文字: 使用浅深绿色底纹或金色下划线，保持精致而不过度抢眼。
+</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>新艺术运动风</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>有机曲线，藤蔓花卉，Mucha 海报感装饰，采用深绿、金色与象牙白调色板，强调优雅、自然与艺术化的流动美感。</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>Web, MiniProgram</t>
+        </is>
+      </c>
+      <c r="W154" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t># Theme Name: 新艺术运动风
+# Vibe &amp; Description:
+有机曲线，藤蔓花卉，Mucha 海报感装饰，采用深绿、金色与象牙白调色板，强调优雅、自然与艺术化的流动美感。
+# Color
+- 使用深绿、金色、象牙白和温暖棕色，避免纯黑、霓虹色和高饱和荧光色。
+- 背景使用象牙白（#F5F0E1）或浅象牙层次（#FAF7EF），文字使用深绿（#2D5016）或深棕色，强调与边框使用金色（#C9A227）。整体配色应像复古展览海报，柔和、精致、带有自然装饰感。
+# Font
+- 使用「思源宋体」作为标题字体。（https://resource-static.bj.bcebos.com/fonts-skill/SourceHanSerifCN-Bold.woff2）
+- 使用「阿里巴巴普惠体3.0」作为正文字体。（https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf）
+# Animation
+- 触摸时元素轻微上浮，并出现柔和的金色光晕，像光线掠过金箔边框。
+- 元素出现时采用缓慢淡入与细微位移，花卉、藤蔓装饰可做低速漂浮或舒展动画，整体节奏保持柔和、优雅。
+# Layout
+- 页面采用非对称构图，标题与装饰图形形成 60/40 的视觉关系，营造复古海报式层次。
+- 卡片与区块保持宽松留白，使用圆角、金色细边框和柔和阴影，移动端以单列为主，局部可加入花卉分隔线增强节奏。
+# Elements
+- 按钮和卡片使用 `rounded-2xl` 或 `rounded-full`，搭配 `border-2 border-[#C9A227]/60` 与柔和阴影。
+- 藤蔓纹样: 用 SVG 或背景图案作为标题、分割线和卡片角落装饰。
+- 花卉边框: 重要区域可加入圆形花卉框或 Mucha 风格拱形装饰。
+- 强调文字: 使用浅深绿色底纹或金色下划线，保持精致而不过度抢眼。</t>
+        </is>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>霓虹科技</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>高饱和霓虹，深色基底，玻璃拟态光晕与彩色渐层叠加，营造现代、活力、前沿的数字科技感。</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="W155" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Theme Name: 霓虹科技
+# Vibe &amp; Description:
+高饱和霓虹，深色基底，玻璃拟态光晕与彩色渐层叠加，营造现代、活力、前沿的数字科技感。
+# Color
+- 使用深紫蓝作为整体背景基底，推荐 `#1e1b4b` 或接近的深色，不使用纯白背景、灰色背景和黑色文字。
+- 主色采用紫色 `#8b5cf6`，搭配青绿 `#06b6d4`、玫红 `#ec4899`、琥珀 `#f59e0b` 作为点缀。
+- 大面积视觉重点使用渐变：`from-violet-500 via-purple-500 to-fuchsia-500`，用于按钮、标题强调、装饰线和关键数字。
+- 卡片使用半透明玻璃效果：`bg-white/10`、`border-white/20`，文字使用 `text-white`、`text-white/80`、`text-white/60` 保持层次。
+# Font
+- 使用「阿里巴巴普惠体3.0」作为标题字体，突出科技感和信息层级。（https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_SemiBold.ttf）
+- 使用「阿里巴巴普惠体3.0」作为正文字体，保持清晰、现代、易读。（https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf）
+## 字体引入方式
+在 `app/_layout.tsx` 中加载字体
+```js
+import { useFonts } from 'expo-font';
+const [fontsLoaded] = useFonts({
+  'AlibabaPuHuiTi-SemiBold': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_SemiBold.ttf' },
+  'AlibabaPuHuiTi-Regular': { uri: 'https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf' },
+});
+```
+`tailwind.config.js` 添加 fontFamily 属性扩展字体
+```js
+{
+  fontFamily: {
+    'alibaba-puhuiti-title': ['AlibabaPuHuiTi-SemiBold', 'sans-serif'],
+    'alibaba-puhuiti-body': ['AlibabaPuHuiTi-Regular', 'sans-serif'],
+  }
+}
+```
+## 字体使用示例
+```jsx
+&lt;Text className="font-alibaba-puhuiti-title text-3xl"&gt;&lt;/Text&gt;
+&lt;Text className="font-alibaba-puhuiti-body text-base"&gt;&lt;/Text&gt;
+```
+# Animation
+- 点击按钮或卡片时使用轻微缩放反馈：`active:scale-95`，并配合彩色阴影增强，形成明确的触摸响应。
+- 元素出现时采用“淡入 + 光晕扩散”效果，渐变装饰可缓慢漂浮，营造动态科技氛围。
+- 所有交互保持顺滑：`transition-all duration-300`，避免生硬位移和传统硬边阴影。
+# Layout
+- 页面以深色全屏背景为基础，顶部可放置简洁 Logo 与主要操作入口，内容以纵向滚动呈现。
+- Hero 区域突出大标题、副标题和主 CTA，背景叠加模糊渐变光晕球，形成视觉焦点。
+- 功能、数据和评价内容使用玻璃卡片纵向排列，卡片间距充足，整体保持清晰的移动端阅读节奏。
+# Elements
+- 按钮使用紫到玫红的渐变背景，圆角为 `rounded-2xl`，配合彩色光晕阴影：`shadow-violet-500/30`。
+- 卡片使用 `rounded-3xl`、半透明背景、细白边框和 `backdrop-blur-xl`，呈现悬浮玻璃质感。
+- 关键数字使用渐变文字效果，标题和图标可加入青绿、淡紫或玫红点缀。
+- 背景装饰使用模糊彩色光斑、渐变线条和半透明叠层，避免实体白卡、黑色文字和尖锐边角。
+</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>王姝睿</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>霓虹科技</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>高饱和霓虹，深色基底，玻璃拟态光晕与彩色渐层叠加，营造现代、活力、前沿的数字科技感。</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>Web, MiniProgram</t>
+        </is>
+      </c>
+      <c r="W156" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t># Theme Name: 霓虹科技
+# Vibe &amp; Description:
+高饱和霓虹，深色基底，玻璃拟态光晕与彩色渐层叠加，营造现代、活力、前沿的数字科技感。
+# Color
+- 使用深紫蓝作为整体背景基底，推荐 `#1e1b4b` 或接近的深色，不使用纯白背景、灰色背景和黑色文字。
+- 主色采用紫色 `#8b5cf6`，搭配青绿 `#06b6d4`、玫红 `#ec4899`、琥珀 `#f59e0b` 作为点缀。
+- 大面积视觉重点使用渐变：`from-violet-500 via-purple-500 to-fuchsia-500`，用于按钮、标题强调、装饰线和关键数字。
+- 卡片使用半透明玻璃效果：`bg-white/10`、`border-white/20`，文字使用 `text-white`、`text-white/80`、`text-white/60` 保持层次。
+# Font
+- 使用「阿里巴巴普惠体3.0」作为标题字体，突出科技感和信息层级。（https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_SemiBold.ttf）
+- 使用「阿里巴巴普惠体3.0」作为正文字体，保持清晰、现代、易读。（https://resource-static.bj.bcebos.com/fonts-skill/AlibabaPuHuiTi_Regular.ttf）
+# Animation
+- 点击按钮或卡片时使用轻微缩放反馈：`active:scale-95`，并配合彩色阴影增强，形成明确的触摸响应。
+- 元素出现时采用“淡入 + 光晕扩散”效果，渐变装饰可缓慢漂浮，营造动态科技氛围。
+- 所有交互保持顺滑：`transition-all duration-300`，避免生硬位移和传统硬边阴影。
+# Layout
+- 页面以深色全屏背景为基础，顶部可放置简洁 Logo 与主要操作入口，内容以纵向滚动呈现。
+- Hero 区域突出大标题、副标题和主 CTA，背景叠加模糊渐变光晕球，形成视觉焦点。
+- 功能、数据和评价内容使用玻璃卡片纵向排列，卡片间距充足，整体保持清晰的移动端阅读节奏。
+# Elements
+- 按钮使用紫到玫红的渐变背景，圆角为 `rounded-2xl`，配合彩色光晕阴影：`shadow-violet-500/30`。
+- 卡片使用 `rounded-3xl`、半透明背景、细白边框和 `backdrop-blur-xl`，呈现悬浮玻璃质感。
+- 关键数字使用渐变文字效果，标题和图标可加入青绿、淡紫或玫红点缀。
+- 背景装饰使用模糊彩色光斑、渐变线条和半透明叠层，避免实体白卡、黑色文字和尖锐边角。</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:17:15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
